--- a/vehicles.xlsx
+++ b/vehicles.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandyeyster/Sandys documents/GEO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{461594F0-2A41-8240-980D-B4940733E977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8160152E-7D57-E54C-BE68-A9D0D8492778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
+    <workbookView xWindow="1060" yWindow="5340" windowWidth="28040" windowHeight="17180" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="51">
   <si>
     <t>Color</t>
   </si>
@@ -44,126 +44,24 @@
     <t>Plate</t>
   </si>
   <si>
-    <t>black</t>
-  </si>
-  <si>
     <t>Ford</t>
   </si>
   <si>
     <t>Chevy</t>
   </si>
   <si>
-    <t>equinox</t>
-  </si>
-  <si>
-    <t>Toyota</t>
-  </si>
-  <si>
     <t>Jeep</t>
   </si>
   <si>
-    <t>Cherokee</t>
-  </si>
-  <si>
     <t>Dodge</t>
   </si>
   <si>
-    <t>Dark</t>
-  </si>
-  <si>
-    <t>grey</t>
-  </si>
-  <si>
-    <t>white</t>
-  </si>
-  <si>
-    <t>dark</t>
-  </si>
-  <si>
-    <t>mitsubizhi</t>
-  </si>
-  <si>
-    <t>Honda</t>
-  </si>
-  <si>
-    <t>Porsche</t>
-  </si>
-  <si>
-    <t>Audi</t>
-  </si>
-  <si>
-    <t>Volvo</t>
-  </si>
-  <si>
-    <t>Ram</t>
-  </si>
-  <si>
-    <t>pinto</t>
-  </si>
-  <si>
-    <t>corolla</t>
-  </si>
-  <si>
-    <t>mirage</t>
-  </si>
-  <si>
-    <t>CRV</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>Durango</t>
-  </si>
-  <si>
     <t>sedan</t>
   </si>
   <si>
     <t>SUV</t>
   </si>
   <si>
-    <t>truck</t>
-  </si>
-  <si>
-    <t>pickup truck</t>
-  </si>
-  <si>
-    <t>van</t>
-  </si>
-  <si>
-    <t>NY:: 357GGG</t>
-  </si>
-  <si>
-    <t>DC: 223333</t>
-  </si>
-  <si>
-    <t>CA: 3335555</t>
-  </si>
-  <si>
-    <t>GA: 88888</t>
-  </si>
-  <si>
-    <t>IL: abcdef</t>
-  </si>
-  <si>
-    <t>GA: 22???</t>
-  </si>
-  <si>
-    <t>MI: LMNOP</t>
-  </si>
-  <si>
-    <t>TN: 22888</t>
-  </si>
-  <si>
-    <t>MD: 88bb33</t>
-  </si>
-  <si>
-    <t>VA: AAA9999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">none: </t>
-  </si>
-  <si>
     <t>note</t>
   </si>
   <si>
@@ -176,43 +74,121 @@
     <t>ID</t>
   </si>
   <si>
-    <t>NY357GGG</t>
-  </si>
-  <si>
-    <t>DC223333</t>
-  </si>
-  <si>
-    <t>CA3335555</t>
-  </si>
-  <si>
-    <t>GA88888</t>
-  </si>
-  <si>
-    <t>ILabcdef</t>
-  </si>
-  <si>
-    <t>GA22???</t>
-  </si>
-  <si>
-    <t>MILMNOP</t>
-  </si>
-  <si>
-    <t>TN22888</t>
-  </si>
-  <si>
-    <t>MD88bb33</t>
-  </si>
-  <si>
-    <t>VAAAA9999</t>
-  </si>
-  <si>
-    <t>none1234</t>
-  </si>
-  <si>
     <t>Model</t>
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Dark grey</t>
+  </si>
+  <si>
+    <t>Nissan</t>
+  </si>
+  <si>
+    <t>Murano</t>
+  </si>
+  <si>
+    <t>TXJGV295</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Malibu</t>
+  </si>
+  <si>
+    <t>DC10697</t>
+  </si>
+  <si>
+    <t>TX JGV295</t>
+  </si>
+  <si>
+    <t>DC 10697</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>DC10674</t>
+  </si>
+  <si>
+    <t>DC 10674</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Explorer</t>
+  </si>
+  <si>
+    <t>VT KMA207</t>
+  </si>
+  <si>
+    <t>VTKMA207</t>
+  </si>
+  <si>
+    <t>Light grey</t>
+  </si>
+  <si>
+    <t>Blazer</t>
+  </si>
+  <si>
+    <t>WIACD389</t>
+  </si>
+  <si>
+    <t>Charger</t>
+  </si>
+  <si>
+    <t>NY HSS7966</t>
+  </si>
+  <si>
+    <t>NYHSS7966</t>
+  </si>
+  <si>
+    <t>MII EUF9371</t>
+  </si>
+  <si>
+    <t>MIEUF9371</t>
+  </si>
+  <si>
+    <t>4x4</t>
+  </si>
+  <si>
+    <t>PA MNC3252</t>
+  </si>
+  <si>
+    <t>PAMNC3252</t>
+  </si>
+  <si>
+    <t>OH EUN4672</t>
+  </si>
+  <si>
+    <t>OHEUN4672</t>
+  </si>
+  <si>
+    <t>Grey</t>
+  </si>
+  <si>
+    <t>Traverse</t>
+  </si>
+  <si>
+    <t>MDHAF908</t>
+  </si>
+  <si>
+    <t>MD HAF908</t>
+  </si>
+  <si>
+    <t>US Marshals placard on dash</t>
+  </si>
+  <si>
+    <t>collaborating MPD</t>
+  </si>
+  <si>
+    <t>WI ACD3891</t>
+  </si>
+  <si>
+    <t>FBI</t>
   </si>
 </sst>
 </file>
@@ -593,418 +569,283 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="G1" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="H1" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>48</v>
       </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="H5" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="H6" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>911</v>
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+      <c r="F7" t="s">
+        <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H7" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
         <v>37</v>
       </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" t="s">
-        <v>52</v>
-      </c>
       <c r="H8" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="H9" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
       <c r="E10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" t="s">
         <v>42</v>
       </c>
-      <c r="G10" t="s">
-        <v>54</v>
-      </c>
       <c r="H10" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H11" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12">
-        <v>1500</v>
-      </c>
-      <c r="D12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="1">
-        <v>46088</v>
-      </c>
+      <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="1">
-        <v>46087</v>
-      </c>
+      <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" s="1">
-        <v>46087</v>
-      </c>
+      <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" t="s">
-        <v>48</v>
-      </c>
-      <c r="H15" s="1">
-        <v>46087</v>
-      </c>
+      <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" t="s">
-        <v>49</v>
-      </c>
-      <c r="H16" s="1">
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17" s="1">
-        <v>46087</v>
-      </c>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/vehicles.xlsx
+++ b/vehicles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandyeyster/Sandys documents/GEO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8160152E-7D57-E54C-BE68-A9D0D8492778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C6C145-DA88-C948-B9AD-3E5B5A890580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="5340" windowWidth="28040" windowHeight="17180" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
+    <workbookView xWindow="7080" yWindow="820" windowWidth="28040" windowHeight="17180" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -89,9 +89,6 @@
     <t>Murano</t>
   </si>
   <si>
-    <t>TXJGV295</t>
-  </si>
-  <si>
     <t>Silver</t>
   </si>
   <si>
@@ -101,9 +98,6 @@
     <t>DC10697</t>
   </si>
   <si>
-    <t>TX JGV295</t>
-  </si>
-  <si>
     <t>DC 10697</t>
   </si>
   <si>
@@ -134,9 +128,6 @@
     <t>Blazer</t>
   </si>
   <si>
-    <t>WIACD389</t>
-  </si>
-  <si>
     <t>Charger</t>
   </si>
   <si>
@@ -146,9 +137,6 @@
     <t>NYHSS7966</t>
   </si>
   <si>
-    <t>MII EUF9371</t>
-  </si>
-  <si>
     <t>MIEUF9371</t>
   </si>
   <si>
@@ -189,6 +177,18 @@
   </si>
   <si>
     <t>FBI</t>
+  </si>
+  <si>
+    <t>WIACD3891</t>
+  </si>
+  <si>
+    <t>MI EUF9371</t>
+  </si>
+  <si>
+    <t>TX JGV2925</t>
+  </si>
+  <si>
+    <t>TXJGV2925</t>
   </si>
 </sst>
 </file>
@@ -601,10 +601,10 @@
         <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="H2" s="1">
         <v>46090</v>
@@ -612,25 +612,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1">
         <v>46090</v>
@@ -638,25 +638,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H4" s="1">
         <v>46090</v>
@@ -664,22 +664,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H5" s="1">
         <v>46090</v>
@@ -687,22 +687,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H6" s="1">
         <v>46090</v>
@@ -716,19 +716,19 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H7" s="1">
         <v>46090</v>
@@ -736,22 +736,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H8" s="1">
         <v>46090</v>
@@ -759,25 +759,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H9" s="1">
         <v>46090</v>
@@ -785,22 +785,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H10" s="1">
         <v>46090</v>
@@ -808,22 +808,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H11" s="1">
         <v>46090</v>

--- a/vehicles.xlsx
+++ b/vehicles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandyeyster/Sandys documents/GEO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA7A72B-9D70-6C44-8ABE-D2EEC0CBF4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C1EAFF-2305-2042-B37B-B1532AA273A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="220" yWindow="1040" windowWidth="28040" windowHeight="17180" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="144">
   <si>
     <t>Color</t>
   </si>
@@ -62,9 +62,15 @@
     <t>Dark</t>
   </si>
   <si>
+    <t>Honda</t>
+  </si>
+  <si>
     <t>Ram</t>
   </si>
   <si>
+    <t>CRV</t>
+  </si>
+  <si>
     <t>sedan</t>
   </si>
   <si>
@@ -429,18 +435,58 @@
   </si>
   <si>
     <t>MD 9EZ7805</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>2 feds</t>
+  </si>
+  <si>
+    <t>MD 6GDE07</t>
+  </si>
+  <si>
+    <t>Rogue</t>
+  </si>
+  <si>
+    <t>PA MZW5585</t>
+  </si>
+  <si>
+    <t>VTKMW207</t>
+  </si>
+  <si>
+    <t>VAVNT4271</t>
+  </si>
+  <si>
+    <t>DC16192</t>
+  </si>
+  <si>
+    <t>MD9EZ7805</t>
+  </si>
+  <si>
+    <t>MD6GDE07</t>
+  </si>
+  <si>
+    <t>PAMZW5585</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -464,11 +510,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -803,50 +851,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC0DC25-20B3-834F-98DA-243C4E7C4E30}">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="G1" s="5" t="s">
         <v>17</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H2" s="1">
         <v>46090</v>
@@ -854,25 +902,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H3" s="1">
         <v>46090</v>
@@ -880,25 +928,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H4" s="1">
         <v>46090</v>
@@ -906,22 +954,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H5" s="1">
         <v>46090</v>
@@ -929,22 +977,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H6" s="1">
         <v>46090</v>
@@ -952,25 +1000,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H7" s="1">
         <v>46090</v>
@@ -978,22 +1026,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H8" s="1">
         <v>46090</v>
@@ -1001,25 +1049,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H9" s="1">
         <v>46090</v>
@@ -1027,22 +1075,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H10" s="1">
         <v>46090</v>
@@ -1050,22 +1098,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H11" s="1">
         <v>46090</v>
@@ -1073,22 +1121,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H12" s="1">
         <v>46091</v>
@@ -1096,19 +1144,19 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H13" s="1">
         <v>46091</v>
@@ -1116,22 +1164,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H14" s="1">
         <v>46091</v>
@@ -1139,19 +1187,19 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H15" s="1">
         <v>46091</v>
@@ -1159,25 +1207,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H16" s="3">
         <v>46091</v>
@@ -1185,23 +1233,23 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H17" s="3">
         <v>46091</v>
@@ -1209,23 +1257,23 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H18" s="3">
         <v>46091</v>
@@ -1233,23 +1281,23 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H19" s="3">
         <v>46091</v>
@@ -1257,23 +1305,23 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H20" s="3">
         <v>46091</v>
@@ -1281,21 +1329,21 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H21" s="3">
         <v>46091</v>
@@ -1303,23 +1351,23 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H22" s="3">
         <v>46091</v>
@@ -1327,23 +1375,23 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H23" s="3">
         <v>46091</v>
@@ -1351,23 +1399,23 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H24" s="3">
         <v>46091</v>
@@ -1375,23 +1423,23 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H25" s="3">
         <v>46091</v>
@@ -1399,23 +1447,23 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H26" s="3">
         <v>46091</v>
@@ -1429,19 +1477,19 @@
         <v>3</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H27" s="3">
         <v>46086</v>
@@ -1449,23 +1497,23 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H28" s="3">
         <v>46086</v>
@@ -1473,23 +1521,23 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H29" s="3">
         <v>46086</v>
@@ -1497,23 +1545,23 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H30" s="3">
         <v>46086</v>
@@ -1521,25 +1569,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H31" s="3">
         <v>46086</v>
@@ -1547,23 +1595,23 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H32" s="3">
         <v>46086</v>
@@ -1571,23 +1619,23 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H33" s="3">
         <v>46086</v>
@@ -1595,25 +1643,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H34" s="3">
         <v>46086</v>
@@ -1621,21 +1669,21 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H35" s="3">
         <v>46086</v>
@@ -1643,21 +1691,21 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H36" s="3">
         <v>46086</v>
@@ -1665,7 +1713,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>5</v>
@@ -1673,13 +1721,13 @@
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="G37" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H37" s="3">
         <v>46086</v>
@@ -1687,23 +1735,23 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H38" s="3">
         <v>46086</v>
@@ -1711,25 +1759,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H39" s="3">
         <v>46086</v>
@@ -1737,23 +1785,23 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H40" s="3">
         <v>46086</v>
@@ -1761,25 +1809,25 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H41" s="3">
         <v>46086</v>
@@ -1787,23 +1835,23 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H42" s="3">
         <v>46086</v>
@@ -1815,17 +1863,17 @@
         <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H43" s="3">
         <v>46086</v>
@@ -1833,139 +1881,151 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G44" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="H44" s="3">
         <v>46087</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
+      <c r="G45" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="H45" s="3">
         <v>46087</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
+      <c r="G46" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="H46" s="3">
         <v>46087</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
+      <c r="G47" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="H47" s="3">
         <v>46087</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
+      <c r="G48" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="H48" s="3">
         <v>46087</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
+      <c r="G49" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="H49" s="3">
         <v>46087</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>5</v>
@@ -1973,103 +2033,368 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
+      <c r="G50" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="H50" s="3">
         <v>46087</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
+      <c r="G51" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="H51" s="3">
         <v>46087</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G52" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="H52" s="3">
         <v>46087</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
+      <c r="G53" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="H53" s="3">
         <v>46087</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
+      <c r="G54" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="H54" s="3">
         <v>46087</v>
       </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" t="s">
+        <v>35</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H55" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56" t="s">
+        <v>55</v>
+      </c>
+      <c r="G56" t="s">
+        <v>56</v>
+      </c>
+      <c r="H56" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>27</v>
+      </c>
+      <c r="B57" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" t="s">
+        <v>63</v>
+      </c>
+      <c r="G57" t="s">
+        <v>64</v>
+      </c>
+      <c r="H57" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>45</v>
+      </c>
+      <c r="B58" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" t="s">
+        <v>35</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>51</v>
+      </c>
+      <c r="G58" t="s">
+        <v>53</v>
+      </c>
+      <c r="H58" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" t="s">
+        <v>127</v>
+      </c>
+      <c r="G59" t="s">
+        <v>139</v>
+      </c>
+      <c r="H59" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B60" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>31</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>79</v>
+      </c>
+      <c r="F60" t="s">
+        <v>134</v>
+      </c>
+      <c r="G60" t="s">
+        <v>80</v>
+      </c>
+      <c r="H60" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>30</v>
+      </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" t="s">
+        <v>36</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>135</v>
+      </c>
+      <c r="G61" t="s">
+        <v>142</v>
+      </c>
+      <c r="H61" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>27</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" t="s">
+        <v>29</v>
+      </c>
+      <c r="G62" t="s">
+        <v>28</v>
+      </c>
+      <c r="H62" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>27</v>
+      </c>
+      <c r="B63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" t="s">
+        <v>72</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s">
+        <v>43</v>
+      </c>
+      <c r="G63" t="s">
+        <v>44</v>
+      </c>
+      <c r="H63" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" t="s">
+        <v>36</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" t="s">
+        <v>54</v>
+      </c>
+      <c r="G64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H64" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>45</v>
+      </c>
+      <c r="B65" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" t="s">
+        <v>136</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" t="s">
+        <v>137</v>
+      </c>
+      <c r="G65" t="s">
+        <v>143</v>
+      </c>
+      <c r="H65" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J70" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/vehicles.xlsx
+++ b/vehicles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandyeyster/Sandys documents/GEO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C1EAFF-2305-2042-B37B-B1532AA273A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24115BE8-ED56-C94B-B269-F5E95E1ED2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="220" yWindow="1040" windowWidth="28040" windowHeight="17180" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="145">
   <si>
     <t>Color</t>
   </si>
@@ -468,6 +468,9 @@
   </si>
   <si>
     <t>PAMZW5585</t>
+  </si>
+  <si>
+    <t>Unconfirmed</t>
   </si>
 </sst>
 </file>
@@ -2381,6 +2384,9 @@
       <c r="E65" t="s">
         <v>137</v>
       </c>
+      <c r="F65" t="s">
+        <v>144</v>
+      </c>
       <c r="G65" t="s">
         <v>143</v>
       </c>

--- a/vehicles.xlsx
+++ b/vehicles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandyeyster/Sandys documents/GEO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF14B2E7-C8A0-7543-8D2D-ABCDA108AD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCED226C-68F1-584A-A181-A9F3F2ABF020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="15980" windowHeight="20100" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="169">
   <si>
     <t>Color</t>
   </si>
@@ -521,12 +521,6 @@
     <t>DEA</t>
   </si>
   <si>
-    <t>??9DKC28</t>
-  </si>
-  <si>
-    <t>?? 9DKC28</t>
-  </si>
-  <si>
     <t>Unconfirmed; seen at 4D substation, may be personal vehicle</t>
   </si>
   <si>
@@ -534,6 +528,24 @@
   </si>
   <si>
     <t>Unconfirmed, seen at 4D station</t>
+  </si>
+  <si>
+    <t>MD9DKC28</t>
+  </si>
+  <si>
+    <t>MD 9DKC28</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>NC WXC6127</t>
+  </si>
+  <si>
+    <t>Highlander</t>
+  </si>
+  <si>
+    <t>NCWXC6127</t>
   </si>
 </sst>
 </file>
@@ -576,11 +588,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -917,32 +927,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC0DC25-20B3-834F-98DA-243C4E7C4E30}">
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1272,943 +1282,904 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="A16" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" t="s">
         <v>69</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="1">
         <v>46091</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="s">
+      <c r="D17" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="1">
         <v>46091</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+      <c r="A18" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="D18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2" t="s">
+      <c r="G18" t="s">
         <v>46</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="1">
         <v>46091</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+      <c r="A19" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2" t="s">
+      <c r="G19" t="s">
         <v>40</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="1">
         <v>46091</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+      <c r="A20" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2" t="s">
+      <c r="G20" t="s">
         <v>30</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="1">
         <v>46091</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+      <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2" t="s">
+      <c r="E21" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2" t="s">
+      <c r="G21" t="s">
         <v>77</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="1">
         <v>46091</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+      <c r="A22" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2" t="s">
+      <c r="G22" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="1">
         <v>46091</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" t="s">
         <v>79</v>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2" t="s">
+      <c r="G23" t="s">
         <v>80</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="1">
         <v>46091</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+      <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2" t="s">
+      <c r="G24" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="1">
         <v>46091</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+      <c r="A25" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2" t="s">
+      <c r="D25" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" t="s">
         <v>83</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" t="s">
         <v>85</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="1">
         <v>46091</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+      <c r="A26" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" t="s">
         <v>3</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" t="s">
         <v>13</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2" t="s">
+      <c r="G26" t="s">
         <v>87</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="1">
         <v>46091</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+      <c r="A27" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" t="s">
         <v>88</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" t="s">
         <v>90</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" t="s">
         <v>99</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
+      <c r="A28" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2" t="s">
+      <c r="G28" t="s">
         <v>35</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
+      <c r="A29" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" t="s">
         <v>39</v>
       </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2" t="s">
+      <c r="G29" t="s">
         <v>40</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
+      <c r="A30" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s">
         <v>81</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2" t="s">
+      <c r="G30" t="s">
         <v>82</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
+      <c r="A31" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" t="s">
         <v>94</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" t="s">
         <v>95</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" t="s">
         <v>114</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" t="s">
         <v>100</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+      <c r="A32" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" t="s">
         <v>98</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2" t="s">
+      <c r="G32" t="s">
         <v>101</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
+      <c r="A33" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" t="s">
         <v>102</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" t="s">
         <v>103</v>
       </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2" t="s">
+      <c r="G33" t="s">
         <v>115</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
+      <c r="A34" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" t="s">
         <v>71</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" t="s">
         <v>72</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
+      <c r="A35" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2" t="s">
+      <c r="E35" t="s">
         <v>105</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" t="s">
         <v>106</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" t="s">
         <v>116</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
+      <c r="A36" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" t="s">
         <v>109</v>
       </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2" t="s">
+      <c r="E36" t="s">
         <v>107</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" t="s">
         <v>108</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" t="s">
         <v>117</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
+      <c r="A37" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2" t="s">
+      <c r="E37" t="s">
         <v>110</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" t="s">
         <v>108</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" t="s">
         <v>118</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
+      <c r="A38" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" t="s">
         <v>64</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" s="2" t="s">
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s">
         <v>65</v>
       </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2" t="s">
+      <c r="G38" t="s">
         <v>66</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H38" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
+      <c r="A39" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" t="s">
         <v>63</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" t="s">
         <v>111</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" t="s">
         <v>112</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" t="s">
         <v>113</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" t="s">
         <v>119</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
+      <c r="A40" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" t="s">
         <v>3</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" t="s">
         <v>26</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" t="s">
         <v>13</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" t="s">
         <v>31</v>
       </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2" t="s">
+      <c r="G40" t="s">
         <v>30</v>
       </c>
-      <c r="H40" s="3">
+      <c r="H40" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
+      <c r="A41" t="s">
         <v>29</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" t="s">
         <v>74</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" s="2" t="s">
+      <c r="D41" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" t="s">
         <v>121</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" t="s">
         <v>46</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
+      <c r="A42" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" t="s">
         <v>120</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" s="2" t="s">
+      <c r="D42" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" t="s">
         <v>142</v>
       </c>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2" t="s">
+      <c r="G42" t="s">
         <v>143</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2" t="s">
+      <c r="B43" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" t="s">
         <v>38</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" t="s">
         <v>56</v>
       </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2" t="s">
+      <c r="G43" t="s">
         <v>41</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
+      <c r="A44" t="s">
         <v>122</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" t="s">
         <v>123</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E44" s="2" t="s">
+      <c r="D44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" t="s">
         <v>98</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" t="s">
         <v>124</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" t="s">
         <v>101</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="1">
         <v>46087</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
+      <c r="A45" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" t="s">
         <v>6</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" t="s">
         <v>13</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" t="s">
         <v>39</v>
       </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2" t="s">
+      <c r="G45" t="s">
         <v>40</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="1">
         <v>46087</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
+      <c r="A46" t="s">
         <v>32</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" t="s">
         <v>2</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" t="s">
         <v>33</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E46" s="2" t="s">
+      <c r="D46" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" t="s">
         <v>34</v>
       </c>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2" t="s">
+      <c r="G46" t="s">
         <v>141</v>
       </c>
-      <c r="H46" s="3">
+      <c r="H46" s="1">
         <v>46087</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
+      <c r="A47" t="s">
         <v>32</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" t="s">
         <v>102</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47" s="2" t="s">
+      <c r="D47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" t="s">
         <v>103</v>
       </c>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2" t="s">
+      <c r="G47" t="s">
         <v>115</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="1">
         <v>46087</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
+      <c r="A48" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" t="s">
         <v>4</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" t="s">
         <v>125</v>
       </c>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2" t="s">
+      <c r="E48" t="s">
         <v>126</v>
       </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2" t="s">
+      <c r="G48" t="s">
         <v>135</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="1">
         <v>46087</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
+      <c r="A49" t="s">
         <v>29</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" t="s">
         <v>63</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" t="s">
         <v>64</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="2" t="s">
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" t="s">
         <v>65</v>
       </c>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2" t="s">
+      <c r="G49" t="s">
         <v>66</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="1">
         <v>46087</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
+      <c r="A50" t="s">
         <v>32</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2" t="s">
+      <c r="E50" t="s">
         <v>110</v>
       </c>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2" t="s">
+      <c r="G50" t="s">
         <v>118</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50" s="1">
         <v>46087</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
+      <c r="A51" t="s">
         <v>29</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" t="s">
         <v>23</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" t="s">
         <v>127</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" t="s">
         <v>13</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" t="s">
         <v>128</v>
       </c>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2" t="s">
+      <c r="G51" t="s">
         <v>136</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="1">
         <v>46087</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
+      <c r="A52" t="s">
         <v>29</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" t="s">
         <v>74</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52" s="2" t="s">
+      <c r="D52" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" t="s">
         <v>45</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" t="s">
         <v>129</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" t="s">
         <v>46</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="1">
         <v>46087</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
+      <c r="A53" t="s">
         <v>32</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" t="s">
         <v>6</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" t="s">
         <v>38</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" t="s">
         <v>13</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" t="s">
         <v>56</v>
       </c>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2" t="s">
+      <c r="G53" t="s">
         <v>41</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H53" s="1">
         <v>46087</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
+      <c r="A54" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" t="s">
         <v>38</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" t="s">
         <v>130</v>
       </c>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2" t="s">
+      <c r="G54" t="s">
         <v>137</v>
       </c>
-      <c r="H54" s="3">
+      <c r="H54" s="1">
         <v>46087</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
+      <c r="A55" t="s">
         <v>36</v>
       </c>
       <c r="B55" t="s">
@@ -2217,13 +2188,13 @@
       <c r="C55" t="s">
         <v>37</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s">
         <v>53</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" t="s">
         <v>55</v>
       </c>
       <c r="H55" s="1">
@@ -2231,7 +2202,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
+      <c r="A56" t="s">
         <v>22</v>
       </c>
       <c r="B56" t="s">
@@ -2260,7 +2231,7 @@
       <c r="C57" t="s">
         <v>64</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" t="s">
         <v>14</v>
       </c>
       <c r="E57" t="s">
@@ -2283,7 +2254,7 @@
       <c r="C58" t="s">
         <v>37</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" t="s">
         <v>14</v>
       </c>
       <c r="E58" t="s">
@@ -2303,7 +2274,7 @@
       <c r="C59" t="s">
         <v>12</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" t="s">
         <v>14</v>
       </c>
       <c r="E59" t="s">
@@ -2323,7 +2294,7 @@
       <c r="C60" t="s">
         <v>33</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" t="s">
         <v>14</v>
       </c>
       <c r="E60" t="s">
@@ -2349,7 +2320,7 @@
       <c r="C61" t="s">
         <v>38</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" t="s">
         <v>13</v>
       </c>
       <c r="E61" t="s">
@@ -2372,7 +2343,7 @@
       <c r="C62" t="s">
         <v>26</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" t="s">
         <v>13</v>
       </c>
       <c r="E62" t="s">
@@ -2395,7 +2366,7 @@
       <c r="C63" t="s">
         <v>74</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" t="s">
         <v>14</v>
       </c>
       <c r="E63" t="s">
@@ -2418,7 +2389,7 @@
       <c r="C64" t="s">
         <v>38</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" t="s">
         <v>13</v>
       </c>
       <c r="E64" t="s">
@@ -2441,7 +2412,7 @@
       <c r="C65" t="s">
         <v>133</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" t="s">
         <v>14</v>
       </c>
       <c r="E65" t="s">
@@ -2467,13 +2438,13 @@
       <c r="C66" t="s">
         <v>37</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="2" t="s">
+      <c r="D66" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" t="s">
         <v>53</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G66" t="s">
         <v>55</v>
       </c>
       <c r="H66" s="1">
@@ -2490,13 +2461,13 @@
       <c r="C67" t="s">
         <v>144</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" t="s">
         <v>13</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="E67" t="s">
         <v>145</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="G67" t="s">
         <v>152</v>
       </c>
       <c r="H67" s="1">
@@ -2513,10 +2484,10 @@
       <c r="C68" t="s">
         <v>125</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="E68" t="s">
         <v>126</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="G68" t="s">
         <v>135</v>
       </c>
       <c r="H68" s="1">
@@ -2536,10 +2507,10 @@
       <c r="D69" t="s">
         <v>14</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="E69" t="s">
         <v>43</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="G69" t="s">
         <v>44</v>
       </c>
       <c r="H69" s="1">
@@ -2559,16 +2530,16 @@
       <c r="D70" t="s">
         <v>14</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="E70" t="s">
         <v>65</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="G70" t="s">
         <v>66</v>
       </c>
       <c r="H70" s="1">
         <v>46093</v>
       </c>
-      <c r="J70" s="4"/>
+      <c r="J70" s="2"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
@@ -2580,10 +2551,10 @@
       <c r="C71" t="s">
         <v>24</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="E71" t="s">
         <v>57</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="G71" t="s">
         <v>58</v>
       </c>
       <c r="H71" s="1">
@@ -2600,10 +2571,10 @@
       <c r="D72" t="s">
         <v>13</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="E72" t="s">
         <v>31</v>
       </c>
-      <c r="G72" s="2" t="s">
+      <c r="G72" t="s">
         <v>30</v>
       </c>
       <c r="H72" s="1">
@@ -2623,10 +2594,10 @@
       <c r="D73" t="s">
         <v>14</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="E73" t="s">
         <v>81</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="G73" t="s">
         <v>82</v>
       </c>
       <c r="H73" s="1">
@@ -2643,10 +2614,10 @@
       <c r="C74" t="s">
         <v>148</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="E74" t="s">
         <v>149</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="G74" t="s">
         <v>153</v>
       </c>
       <c r="H74" s="1">
@@ -2666,10 +2637,10 @@
       <c r="D75" t="s">
         <v>13</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="E75" t="s">
         <v>150</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G75" t="s">
         <v>154</v>
       </c>
       <c r="H75" s="1">
@@ -2689,10 +2660,10 @@
       <c r="D76" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E76" t="s">
         <v>45</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" t="s">
         <v>46</v>
       </c>
       <c r="H76" s="1">
@@ -2712,10 +2683,10 @@
       <c r="D77" t="s">
         <v>13</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E77" t="s">
         <v>132</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="G77" t="s">
         <v>138</v>
       </c>
       <c r="H77" s="1">
@@ -2735,13 +2706,13 @@
       <c r="D78" t="s">
         <v>14</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="E78" t="s">
         <v>134</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="F78" t="s">
         <v>151</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G78" t="s">
         <v>139</v>
       </c>
       <c r="H78" s="1">
@@ -2758,10 +2729,10 @@
       <c r="D79" t="s">
         <v>14</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="E79" t="s">
         <v>155</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="G79" t="s">
         <v>157</v>
       </c>
       <c r="H79" s="1">
@@ -2778,10 +2749,10 @@
       <c r="D80" t="s">
         <v>14</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="E80" t="s">
         <v>156</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G80" t="s">
         <v>158</v>
       </c>
       <c r="H80" s="1">
@@ -2801,10 +2772,10 @@
       <c r="D81" t="s">
         <v>14</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="E81" t="s">
         <v>81</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="G81" t="s">
         <v>82</v>
       </c>
       <c r="H81" s="1">
@@ -2821,13 +2792,13 @@
       <c r="C82" t="s">
         <v>24</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="E82" t="s">
         <v>57</v>
       </c>
-      <c r="F82" s="2" t="s">
+      <c r="F82" t="s">
         <v>159</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="G82" t="s">
         <v>58</v>
       </c>
       <c r="H82" s="1">
@@ -2847,10 +2818,10 @@
       <c r="D83" t="s">
         <v>13</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="E83" t="s">
         <v>132</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="G83" t="s">
         <v>138</v>
       </c>
       <c r="H83" s="1">
@@ -2870,10 +2841,10 @@
       <c r="D84" t="s">
         <v>14</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="E84" t="s">
         <v>43</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G84" t="s">
         <v>44</v>
       </c>
       <c r="H84" s="1">
@@ -2893,14 +2864,14 @@
       <c r="D85" t="s">
         <v>13</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G85" s="2" t="s">
+      <c r="E85" t="s">
+        <v>164</v>
+      </c>
+      <c r="F85" t="s">
         <v>160</v>
+      </c>
+      <c r="G85" t="s">
+        <v>163</v>
       </c>
       <c r="H85" s="1">
         <v>46094</v>
@@ -2919,13 +2890,13 @@
       <c r="D86" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="2" t="s">
+      <c r="E86" t="s">
         <v>65</v>
       </c>
-      <c r="F86" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="G86" s="2" t="s">
+      <c r="F86" t="s">
+        <v>161</v>
+      </c>
+      <c r="G86" t="s">
         <v>66</v>
       </c>
       <c r="H86" s="1">
@@ -2942,19 +2913,68 @@
       <c r="C87" t="s">
         <v>37</v>
       </c>
-      <c r="D87" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" s="2" t="s">
+      <c r="D87" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" t="s">
         <v>53</v>
       </c>
-      <c r="F87" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G87" s="2" t="s">
+      <c r="F87" t="s">
+        <v>162</v>
+      </c>
+      <c r="G87" t="s">
         <v>55</v>
       </c>
       <c r="H87" s="1">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>165</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" t="s">
+        <v>167</v>
+      </c>
+      <c r="D88" t="s">
+        <v>14</v>
+      </c>
+      <c r="E88" t="s">
+        <v>166</v>
+      </c>
+      <c r="F88" t="s">
+        <v>140</v>
+      </c>
+      <c r="G88" t="s">
+        <v>168</v>
+      </c>
+      <c r="H88" s="1">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>73</v>
+      </c>
+      <c r="B89" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" t="s">
+        <v>42</v>
+      </c>
+      <c r="D89" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" t="s">
+        <v>45</v>
+      </c>
+      <c r="G89" t="s">
+        <v>46</v>
+      </c>
+      <c r="H89" s="1">
         <v>46094</v>
       </c>
     </row>

--- a/vehicles.xlsx
+++ b/vehicles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandyeyster/Sandys documents/GEO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCED226C-68F1-584A-A181-A9F3F2ABF020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD8412C7-C79B-9C46-AD53-C5A2BC6A05F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="15980" windowHeight="20100" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
+    <workbookView xWindow="920" yWindow="600" windowWidth="15980" windowHeight="20100" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/vehicles.xlsx
+++ b/vehicles.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandyeyster/Sandys documents/GEO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A108ED90-CB75-6C46-B8CF-9A84AC71779A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F80832-5739-9042-B669-7869D799999D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="620" windowWidth="15980" windowHeight="20100" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$163</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="279">
   <si>
     <t>Color</t>
   </si>
@@ -476,9 +476,6 @@
     <t>Camry</t>
   </si>
   <si>
-    <t>NJ X87VNX</t>
-  </si>
-  <si>
     <t>Compass</t>
   </si>
   <si>
@@ -497,9 +494,6 @@
     <t xml:space="preserve">unconfirmed. </t>
   </si>
   <si>
-    <t>NJX87VNX</t>
-  </si>
-  <si>
     <t>MD8GK7048</t>
   </si>
   <si>
@@ -644,28 +638,16 @@
     <t>PALGC5235</t>
   </si>
   <si>
-    <t>CH-R</t>
-  </si>
-  <si>
-    <t>light</t>
-  </si>
-  <si>
     <t>MPD undercover</t>
   </si>
   <si>
     <t>(CBP, other feds)</t>
   </si>
   <si>
-    <t>PA NMC3252</t>
-  </si>
-  <si>
     <t>NJ X87VNZ</t>
   </si>
   <si>
     <t>OH EUN4762</t>
-  </si>
-  <si>
-    <t>PANMC3252</t>
   </si>
   <si>
     <t>NJX87VNZ</t>
@@ -1275,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC0DC25-20B3-834F-98DA-243C4E7C4E30}">
-  <dimension ref="A1:L187"/>
+  <dimension ref="A1:L171"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -1306,580 +1288,562 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>167</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>174</v>
       </c>
       <c r="G2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="H2" s="1">
-        <v>46090</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
+        <v>183</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>52</v>
+        <v>185</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>188</v>
       </c>
       <c r="H3" s="1">
-        <v>46090</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>168</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" t="s">
-        <v>52</v>
+        <v>178</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="H4" s="1">
-        <v>46090</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="H5" s="1">
-        <v>46090</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>168</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>98</v>
+      </c>
+      <c r="F6" t="s">
+        <v>173</v>
       </c>
       <c r="G6" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="H6" s="1">
-        <v>46090</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>169</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="H7" s="1">
-        <v>46090</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>175</v>
       </c>
       <c r="H8" s="1">
-        <v>46090</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>186</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>184</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="H9" s="1">
-        <v>46090</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="H10" s="1">
-        <v>46090</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>226</v>
       </c>
       <c r="H11" s="1">
-        <v>46090</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>167</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H12" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>213</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>219</v>
+      </c>
+      <c r="F13" t="s">
+        <v>214</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>224</v>
       </c>
       <c r="H13" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H14" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>205</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>96</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="H15" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" t="s">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" t="s">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="G16" t="s">
-        <v>69</v>
+        <v>227</v>
       </c>
       <c r="H16" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>171</v>
       </c>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" t="s">
-        <v>70</v>
+        <v>212</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>228</v>
       </c>
       <c r="H17" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H18" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>218</v>
+      </c>
+      <c r="F19" t="s">
+        <v>193</v>
       </c>
       <c r="G19" t="s">
-        <v>40</v>
+        <v>223</v>
       </c>
       <c r="H19" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>171</v>
       </c>
       <c r="B20" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G20" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H20" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>168</v>
       </c>
       <c r="B21" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>76</v>
+        <v>217</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="H21" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>215</v>
       </c>
       <c r="G22" t="s">
-        <v>41</v>
+        <v>220</v>
       </c>
       <c r="H22" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>192</v>
       </c>
       <c r="B23" t="s">
         <v>2</v>
       </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H23" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="B24" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>216</v>
       </c>
       <c r="G24" t="s">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="H24" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="G25" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="H25" s="1">
-        <v>46091</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>105</v>
+      </c>
+      <c r="F26" t="s">
+        <v>106</v>
       </c>
       <c r="G26" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="H26" s="1">
-        <v>46091</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -1910,22 +1874,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G28" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H28" s="1">
         <v>46086</v>
@@ -1933,22 +1897,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
-        <v>39</v>
+        <v>107</v>
+      </c>
+      <c r="F29" t="s">
+        <v>108</v>
       </c>
       <c r="G29" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="H29" s="1">
         <v>46086</v>
@@ -1956,22 +1917,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="G30" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="H30" s="1">
         <v>46086</v>
@@ -1979,25 +1940,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="F31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G31" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="H31" s="1">
         <v>46086</v>
@@ -2005,22 +1966,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>98</v>
+        <v>71</v>
+      </c>
+      <c r="F32" t="s">
+        <v>106</v>
       </c>
       <c r="G32" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="H32" s="1">
         <v>46086</v>
@@ -2028,22 +1992,19 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>103</v>
+        <v>110</v>
+      </c>
+      <c r="F33" t="s">
+        <v>108</v>
       </c>
       <c r="G33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H33" s="1">
         <v>46086</v>
@@ -2051,45 +2012,42 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="B34" t="s">
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E34" t="s">
-        <v>71</v>
-      </c>
-      <c r="F34" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G34" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="H34" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>47</v>
-      </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>6</v>
+      </c>
+      <c r="C35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>105</v>
-      </c>
-      <c r="F35" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="G35" t="s">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="H35" s="1">
         <v>46086</v>
@@ -2097,19 +2055,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>96</v>
+      </c>
+      <c r="D36" t="s">
+        <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>107</v>
-      </c>
-      <c r="F36" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="G36" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="H36" s="1">
         <v>46086</v>
@@ -2117,19 +2078,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>110</v>
-      </c>
-      <c r="F37" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="G37" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="H37" s="1">
         <v>46086</v>
@@ -2140,19 +2104,22 @@
         <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="D38" t="s">
         <v>14</v>
       </c>
       <c r="E38" t="s">
-        <v>65</v>
+        <v>45</v>
+      </c>
+      <c r="F38" t="s">
+        <v>121</v>
       </c>
       <c r="G38" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="H38" s="1">
         <v>46086</v>
@@ -2160,25 +2127,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E39" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="F39" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G39" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="H39" s="1">
         <v>46086</v>
@@ -2189,19 +2156,19 @@
         <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="G40" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="H40" s="1">
         <v>46086</v>
@@ -2209,25 +2176,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="C41" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="D41" t="s">
         <v>14</v>
       </c>
       <c r="E41" t="s">
-        <v>45</v>
-      </c>
-      <c r="F41" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="H41" s="1">
         <v>46086</v>
@@ -2235,68 +2199,62 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B42" t="s">
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="D42" t="s">
         <v>14</v>
       </c>
       <c r="E42" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="G42" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="H42" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="G43" t="s">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="H43" s="1">
-        <v>46086</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>123</v>
-      </c>
-      <c r="C44" t="s">
-        <v>96</v>
-      </c>
-      <c r="D44" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>98</v>
-      </c>
-      <c r="F44" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="G44" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="H44" s="1">
         <v>46087</v>
@@ -2307,19 +2265,19 @@
         <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="G45" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="H45" s="1">
         <v>46087</v>
@@ -2327,22 +2285,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="G46" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H46" s="1">
         <v>46087</v>
@@ -2353,19 +2311,19 @@
         <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="G47" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="H47" s="1">
         <v>46087</v>
@@ -2373,19 +2331,25 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="B48" t="s">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>125</v>
+        <v>96</v>
+      </c>
+      <c r="D48" t="s">
+        <v>14</v>
       </c>
       <c r="E48" t="s">
-        <v>126</v>
+        <v>98</v>
+      </c>
+      <c r="F48" t="s">
+        <v>124</v>
       </c>
       <c r="G48" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="H48" s="1">
         <v>46087</v>
@@ -2393,22 +2357,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="G49" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="H49" s="1">
         <v>46087</v>
@@ -2416,16 +2380,25 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B50" t="s">
         <v>5</v>
       </c>
+      <c r="C50" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" t="s">
+        <v>14</v>
+      </c>
       <c r="E50" t="s">
-        <v>110</v>
+        <v>45</v>
+      </c>
+      <c r="F50" t="s">
+        <v>129</v>
       </c>
       <c r="G50" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="H50" s="1">
         <v>46087</v>
@@ -2436,19 +2409,19 @@
         <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="C51" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E51" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="G51" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="H51" s="1">
         <v>46087</v>
@@ -2456,25 +2429,19 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>74</v>
-      </c>
-      <c r="D52" t="s">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="E52" t="s">
-        <v>45</v>
-      </c>
-      <c r="F52" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G52" t="s">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="H52" s="1">
         <v>46087</v>
@@ -2485,19 +2452,19 @@
         <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D53" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E53" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="G53" t="s">
-        <v>41</v>
+        <v>141</v>
       </c>
       <c r="H53" s="1">
         <v>46087</v>
@@ -2505,278 +2472,275 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>22</v>
+        <v>171</v>
       </c>
       <c r="B54" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" t="s">
-        <v>130</v>
-      </c>
-      <c r="G54" t="s">
-        <v>137</v>
+        <v>14</v>
+      </c>
+      <c r="E54">
+        <v>23616</v>
+      </c>
+      <c r="F54" t="s">
+        <v>206</v>
+      </c>
+      <c r="G54">
+        <v>23616</v>
       </c>
       <c r="H54" s="1">
-        <v>46087</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>36</v>
-      </c>
-      <c r="B55" t="s">
-        <v>3</v>
-      </c>
-      <c r="C55" t="s">
-        <v>37</v>
+        <v>205</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E55" t="s">
-        <v>53</v>
+        <v>207</v>
       </c>
       <c r="G55" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="H55" s="1">
-        <v>46092</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B56" t="s">
-        <v>23</v>
-      </c>
-      <c r="C56" t="s">
-        <v>24</v>
+        <v>5</v>
+      </c>
+      <c r="D56" t="s">
+        <v>14</v>
       </c>
       <c r="E56" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="G56" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="H56" s="1">
-        <v>46092</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>29</v>
+        <v>205</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="C57" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D57" t="s">
         <v>14</v>
       </c>
       <c r="E57" t="s">
-        <v>65</v>
+        <v>98</v>
+      </c>
+      <c r="F57" t="s">
+        <v>173</v>
       </c>
       <c r="G57" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="H57" s="1">
-        <v>46092</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>47</v>
+        <v>168</v>
       </c>
       <c r="B58" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="G58" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H58" s="1">
-        <v>46092</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>32</v>
+      </c>
       <c r="B59" t="s">
-        <v>9</v>
-      </c>
-      <c r="C59" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D59" t="s">
         <v>14</v>
       </c>
       <c r="E59" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="G59" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="H59" s="1">
-        <v>46092</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>171</v>
+      </c>
       <c r="B60" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="D60" t="s">
         <v>14</v>
       </c>
       <c r="E60" t="s">
-        <v>81</v>
-      </c>
-      <c r="F60" t="s">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="G60" t="s">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="H60" s="1">
-        <v>46092</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
       <c r="B61" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D61" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="G61" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="H61" s="1">
-        <v>46092</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>29</v>
+        <v>168</v>
       </c>
       <c r="B62" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D62" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G62" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H62" s="1">
-        <v>46092</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="B63" t="s">
         <v>5</v>
       </c>
-      <c r="C63" t="s">
-        <v>74</v>
-      </c>
       <c r="D63" t="s">
         <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>45</v>
+        <v>208</v>
       </c>
       <c r="G63" t="s">
-        <v>46</v>
+        <v>210</v>
       </c>
       <c r="H63" s="1">
-        <v>46092</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B64" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D64" t="s">
         <v>13</v>
       </c>
       <c r="E64" t="s">
-        <v>56</v>
+        <v>31</v>
+      </c>
+      <c r="F64" t="s">
+        <v>52</v>
       </c>
       <c r="G64" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H64" s="1">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>133</v>
+        <v>26</v>
       </c>
       <c r="D65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E65" t="s">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="F65" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="G65" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="H65" s="1">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>47</v>
       </c>
@@ -2784,65 +2748,71 @@
         <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D66" t="s">
         <v>14</v>
       </c>
       <c r="E66" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G66" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H66" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="D67" t="s">
         <v>13</v>
       </c>
       <c r="E67" t="s">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="G67" t="s">
-        <v>152</v>
+        <v>41</v>
       </c>
       <c r="H67" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B68" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C68" t="s">
-        <v>125</v>
+        <v>38</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
       </c>
       <c r="E68" t="s">
-        <v>126</v>
+        <v>39</v>
+      </c>
+      <c r="F68" t="s">
+        <v>54</v>
       </c>
       <c r="G68" t="s">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="H68" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>29</v>
       </c>
@@ -2850,46 +2820,48 @@
         <v>5</v>
       </c>
       <c r="C69" t="s">
-        <v>147</v>
+        <v>42</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
       </c>
       <c r="E69" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G69" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H69" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>29</v>
       </c>
       <c r="B70" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="C70" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D70" t="s">
         <v>14</v>
       </c>
       <c r="E70" t="s">
-        <v>65</v>
+        <v>43</v>
+      </c>
+      <c r="F70" t="s">
+        <v>51</v>
       </c>
       <c r="G70" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="H70" s="1">
-        <v>46093</v>
-      </c>
-      <c r="J70" s="2"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>22</v>
       </c>
@@ -2906,274 +2878,283 @@
         <v>58</v>
       </c>
       <c r="H71" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
+        <v>32</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2</v>
+      </c>
+      <c r="C72" t="s">
+        <v>33</v>
+      </c>
+      <c r="D72" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" t="s">
+        <v>34</v>
+      </c>
+      <c r="G72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H72" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>36</v>
+      </c>
+      <c r="B73" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" t="s">
+        <v>53</v>
+      </c>
+      <c r="G73" t="s">
+        <v>55</v>
+      </c>
+      <c r="H73" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
         <v>29</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B74" t="s">
         <v>3</v>
       </c>
-      <c r="D72" t="s">
-        <v>13</v>
-      </c>
-      <c r="E72" t="s">
+      <c r="C74" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" t="s">
         <v>31</v>
       </c>
-      <c r="G72" t="s">
+      <c r="G74" t="s">
         <v>30</v>
       </c>
-      <c r="H72" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>32</v>
-      </c>
-      <c r="B73" t="s">
-        <v>2</v>
-      </c>
-      <c r="C73" t="s">
-        <v>33</v>
-      </c>
-      <c r="D73" t="s">
-        <v>14</v>
-      </c>
-      <c r="E73" t="s">
-        <v>81</v>
-      </c>
-      <c r="G73" t="s">
-        <v>82</v>
-      </c>
-      <c r="H73" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>22</v>
-      </c>
-      <c r="B74" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" t="s">
-        <v>148</v>
-      </c>
-      <c r="E74" t="s">
-        <v>149</v>
-      </c>
-      <c r="G74" t="s">
-        <v>153</v>
-      </c>
       <c r="H74" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>47</v>
       </c>
       <c r="B75" t="s">
-        <v>23</v>
-      </c>
-      <c r="C75" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="D75" t="s">
         <v>13</v>
       </c>
       <c r="E75" t="s">
-        <v>150</v>
+        <v>84</v>
+      </c>
+      <c r="F75" t="s">
+        <v>83</v>
       </c>
       <c r="G75" t="s">
-        <v>154</v>
+        <v>85</v>
       </c>
       <c r="H75" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E76" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="G76" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="H76" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>32</v>
       </c>
       <c r="B77" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" t="s">
+        <v>67</v>
+      </c>
+      <c r="D77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" t="s">
+        <v>68</v>
+      </c>
+      <c r="F77" t="s">
+        <v>70</v>
+      </c>
+      <c r="G77" t="s">
+        <v>69</v>
+      </c>
+      <c r="H77" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" t="s">
+        <v>71</v>
+      </c>
+      <c r="F78" t="s">
+        <v>70</v>
+      </c>
+      <c r="G78" t="s">
+        <v>72</v>
+      </c>
+      <c r="H78" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" t="s">
+        <v>2</v>
+      </c>
+      <c r="C79" t="s">
+        <v>78</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>79</v>
+      </c>
+      <c r="G79" t="s">
+        <v>80</v>
+      </c>
+      <c r="H79" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>32</v>
+      </c>
+      <c r="B80" t="s">
         <v>6</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C80" t="s">
         <v>38</v>
       </c>
-      <c r="D77" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" t="s">
-        <v>132</v>
-      </c>
-      <c r="G77" t="s">
-        <v>138</v>
-      </c>
-      <c r="H77" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>47</v>
-      </c>
-      <c r="B78" t="s">
-        <v>23</v>
-      </c>
-      <c r="C78" t="s">
-        <v>133</v>
-      </c>
-      <c r="D78" t="s">
-        <v>14</v>
-      </c>
-      <c r="E78" t="s">
-        <v>134</v>
-      </c>
-      <c r="F78" t="s">
-        <v>151</v>
-      </c>
-      <c r="G78" t="s">
-        <v>139</v>
-      </c>
-      <c r="H78" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>32</v>
-      </c>
-      <c r="B79" t="s">
-        <v>23</v>
-      </c>
-      <c r="D79" t="s">
-        <v>14</v>
-      </c>
-      <c r="E79" t="s">
-        <v>155</v>
-      </c>
-      <c r="G79" t="s">
-        <v>157</v>
-      </c>
-      <c r="H79" s="1">
-        <v>46089</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>47</v>
-      </c>
-      <c r="B80" t="s">
-        <v>5</v>
-      </c>
       <c r="D80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E80" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="G80" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="H80" s="1">
-        <v>46089</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B81" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C81" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E81" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="G81" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="H81" s="1">
-        <v>46094</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="B82" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>74</v>
+      </c>
+      <c r="D82" t="s">
+        <v>14</v>
       </c>
       <c r="E82" t="s">
-        <v>57</v>
-      </c>
-      <c r="F82" t="s">
-        <v>159</v>
+        <v>45</v>
       </c>
       <c r="G82" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="H82" s="1">
-        <v>46094</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B83" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="C83" t="s">
-        <v>38</v>
-      </c>
-      <c r="D83" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="G83" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="H83" s="1">
-        <v>46094</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -3181,562 +3162,556 @@
         <v>29</v>
       </c>
       <c r="B84" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C84" t="s">
-        <v>146</v>
-      </c>
-      <c r="D84" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="E84" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="G84" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="H84" s="1">
-        <v>46094</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B85" t="s">
-        <v>94</v>
-      </c>
-      <c r="C85">
-        <v>200</v>
-      </c>
-      <c r="D85" t="s">
-        <v>13</v>
+        <v>63</v>
+      </c>
+      <c r="C85" t="s">
+        <v>64</v>
       </c>
       <c r="E85" t="s">
-        <v>164</v>
-      </c>
-      <c r="F85" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="G85" t="s">
-        <v>163</v>
+        <v>66</v>
       </c>
       <c r="H85" s="1">
-        <v>46094</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B86" t="s">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="C86" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D86" t="s">
         <v>14</v>
       </c>
       <c r="E86" t="s">
-        <v>65</v>
-      </c>
-      <c r="F86" t="s">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="G86" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H86" s="1">
-        <v>46094</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B87" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C87" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D87" t="s">
         <v>14</v>
       </c>
       <c r="E87" t="s">
-        <v>53</v>
-      </c>
-      <c r="F87" t="s">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="G87" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H87" s="1">
-        <v>46094</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>165</v>
+        <v>59</v>
       </c>
       <c r="B88" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>167</v>
+        <v>37</v>
       </c>
       <c r="D88" t="s">
         <v>14</v>
       </c>
       <c r="E88" t="s">
-        <v>166</v>
-      </c>
-      <c r="F88" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="G88" t="s">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="H88" s="1">
-        <v>46094</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="B89" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E89" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G89" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H89" s="1">
-        <v>46094</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>32</v>
       </c>
       <c r="B90" t="s">
-        <v>63</v>
+        <v>6</v>
+      </c>
+      <c r="C90" t="s">
+        <v>38</v>
       </c>
       <c r="D90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E90" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="G90" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="H90" s="1">
-        <v>46083</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="B91" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="C91" t="s">
+        <v>38</v>
       </c>
       <c r="D91" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E91" t="s">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="G91" t="s">
-        <v>178</v>
+        <v>41</v>
       </c>
       <c r="H91" s="1">
-        <v>46083</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="B92" t="s">
-        <v>23</v>
+        <v>5</v>
+      </c>
+      <c r="C92" t="s">
+        <v>74</v>
       </c>
       <c r="D92" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E92" t="s">
-        <v>181</v>
-      </c>
-      <c r="F92" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="G92" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="H92" s="1">
-        <v>46083</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>172</v>
+        <v>23</v>
       </c>
       <c r="C93" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="D93" t="s">
         <v>14</v>
       </c>
       <c r="E93" t="s">
-        <v>183</v>
+        <v>134</v>
+      </c>
+      <c r="F93" t="s">
+        <v>140</v>
       </c>
       <c r="G93" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="H93" s="1">
-        <v>46083</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>170</v>
+        <v>22</v>
       </c>
       <c r="B94" t="s">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="C94" t="s">
-        <v>96</v>
-      </c>
-      <c r="D94" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E94" t="s">
-        <v>98</v>
-      </c>
-      <c r="F94" t="s">
-        <v>175</v>
+        <v>57</v>
       </c>
       <c r="G94" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="H94" s="1">
-        <v>46083</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>169</v>
+        <v>29</v>
       </c>
       <c r="B95" t="s">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="C95" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="D95" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E95" t="s">
-        <v>28</v>
-      </c>
-      <c r="F95" t="s">
-        <v>176</v>
+        <v>65</v>
       </c>
       <c r="G95" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H95" s="1">
-        <v>46083</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>8</v>
-      </c>
       <c r="B96" t="s">
-        <v>185</v>
+        <v>2</v>
+      </c>
+      <c r="C96" t="s">
+        <v>33</v>
       </c>
       <c r="D96" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E96" t="s">
-        <v>187</v>
+        <v>81</v>
+      </c>
+      <c r="F96" t="s">
+        <v>131</v>
       </c>
       <c r="G96" t="s">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="H96" s="1">
-        <v>46083</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>169</v>
-      </c>
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B97" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C97" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D97" t="s">
         <v>14</v>
       </c>
       <c r="E97" t="s">
-        <v>188</v>
-      </c>
-      <c r="F97" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="G97" t="s">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="H97" s="1">
-        <v>46083</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="B98" t="s">
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="D98" t="s">
         <v>14</v>
       </c>
       <c r="E98" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="G98" t="s">
-        <v>192</v>
+        <v>55</v>
       </c>
       <c r="H98" s="1">
-        <v>46083</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B99" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" t="s">
+        <v>30</v>
+      </c>
+      <c r="F99" t="s">
+        <v>199</v>
+      </c>
+      <c r="G99" t="s">
+        <v>30</v>
+      </c>
+      <c r="H99" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" t="s">
+        <v>23</v>
+      </c>
+      <c r="C100" t="s">
+        <v>127</v>
+      </c>
+      <c r="D100" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" t="s">
+        <v>149</v>
+      </c>
+      <c r="F100" t="s">
+        <v>193</v>
+      </c>
+      <c r="G100" t="s">
+        <v>152</v>
+      </c>
+      <c r="H100" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>168</v>
+      </c>
+      <c r="B101" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" t="s">
+        <v>38</v>
+      </c>
+      <c r="D101" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" t="s">
+        <v>132</v>
+      </c>
+      <c r="F101" t="s">
+        <v>193</v>
+      </c>
+      <c r="G101" t="s">
+        <v>138</v>
+      </c>
+      <c r="H101" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>169</v>
+      </c>
+      <c r="B102" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" t="s">
+        <v>147</v>
+      </c>
+      <c r="D102" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" t="s">
+        <v>148</v>
+      </c>
+      <c r="G102" t="s">
+        <v>151</v>
+      </c>
+      <c r="H102" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>171</v>
+      </c>
+      <c r="B103" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" t="s">
+        <v>144</v>
+      </c>
+      <c r="D103" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" t="s">
+        <v>201</v>
+      </c>
+      <c r="G103" t="s">
+        <v>203</v>
+      </c>
+      <c r="H103" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>171</v>
+      </c>
+      <c r="B104" t="s">
         <v>5</v>
       </c>
-      <c r="D99" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="D104" t="s">
+        <v>14</v>
+      </c>
+      <c r="E104" t="s">
+        <v>202</v>
+      </c>
+      <c r="G104" t="s">
+        <v>204</v>
+      </c>
+      <c r="H104" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>29</v>
+      </c>
+      <c r="B105" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" t="s">
+        <v>146</v>
+      </c>
+      <c r="D105" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" t="s">
         <v>43</v>
       </c>
-      <c r="G99" t="s">
+      <c r="G105" t="s">
         <v>44</v>
-      </c>
-      <c r="H99" s="1">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
-        <v>173</v>
-      </c>
-      <c r="B100" t="s">
-        <v>3</v>
-      </c>
-      <c r="C100" t="s">
-        <v>26</v>
-      </c>
-      <c r="D100" t="s">
-        <v>13</v>
-      </c>
-      <c r="E100" t="s">
-        <v>31</v>
-      </c>
-      <c r="G100" t="s">
-        <v>30</v>
-      </c>
-      <c r="H100" s="1">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>173</v>
-      </c>
-      <c r="B101" t="s">
-        <v>5</v>
-      </c>
-      <c r="D101" t="s">
-        <v>14</v>
-      </c>
-      <c r="E101" t="s">
-        <v>45</v>
-      </c>
-      <c r="G101" t="s">
-        <v>46</v>
-      </c>
-      <c r="H101" s="1">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>194</v>
-      </c>
-      <c r="B102" t="s">
-        <v>62</v>
-      </c>
-      <c r="C102" t="s">
-        <v>193</v>
-      </c>
-      <c r="D102" t="s">
-        <v>14</v>
-      </c>
-      <c r="E102" t="s">
-        <v>199</v>
-      </c>
-      <c r="F102" t="s">
-        <v>195</v>
-      </c>
-      <c r="G102" t="s">
-        <v>198</v>
-      </c>
-      <c r="H102" s="1">
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
-        <v>8</v>
-      </c>
-      <c r="B103" t="s">
-        <v>62</v>
-      </c>
-      <c r="C103" t="s">
-        <v>24</v>
-      </c>
-      <c r="D103" t="s">
-        <v>14</v>
-      </c>
-      <c r="E103" t="s">
-        <v>57</v>
-      </c>
-      <c r="G103" t="s">
-        <v>58</v>
-      </c>
-      <c r="H103" s="1">
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
-        <v>194</v>
-      </c>
-      <c r="D104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" t="s">
-        <v>197</v>
-      </c>
-      <c r="F104" t="s">
-        <v>196</v>
-      </c>
-      <c r="G104" t="s">
-        <v>200</v>
-      </c>
-      <c r="H104" s="1">
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>8</v>
-      </c>
-      <c r="B105" t="s">
-        <v>4</v>
-      </c>
-      <c r="C105" t="s">
-        <v>201</v>
-      </c>
-      <c r="D105" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" t="s">
-        <v>126</v>
-      </c>
-      <c r="G105" t="s">
-        <v>135</v>
       </c>
       <c r="H105" s="1">
         <v>46093</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="B106" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C106" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="D106" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E106" t="s">
-        <v>149</v>
+        <v>134</v>
+      </c>
+      <c r="F106" t="s">
+        <v>150</v>
       </c>
       <c r="G106" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="H106" s="1">
         <v>46093</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>173</v>
+        <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C107" t="s">
-        <v>146</v>
+        <v>24</v>
       </c>
       <c r="D107" t="s">
         <v>14</v>
       </c>
       <c r="E107" t="s">
-        <v>205</v>
+        <v>57</v>
+      </c>
+      <c r="F107" t="s">
+        <v>157</v>
       </c>
       <c r="G107" t="s">
-        <v>208</v>
+        <v>58</v>
       </c>
       <c r="H107" s="1">
         <v>46093</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>173</v>
+        <v>29</v>
       </c>
       <c r="B108" t="s">
         <v>63</v>
@@ -3756,59 +3731,57 @@
       <c r="H108" s="1">
         <v>46093</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J108" s="2"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>8</v>
+        <v>168</v>
       </c>
       <c r="B109" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C109" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D109" t="s">
         <v>14</v>
       </c>
       <c r="E109" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="F109" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="G109" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="H109" s="1">
         <v>46093</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>173</v>
+        <v>8</v>
       </c>
       <c r="B110" t="s">
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>144</v>
-      </c>
-      <c r="D110" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="E110" t="s">
-        <v>206</v>
+        <v>126</v>
       </c>
       <c r="G110" t="s">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="H110" s="1">
         <v>46093</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B111" t="s">
         <v>3</v>
@@ -3829,474 +3802,510 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>173</v>
+        <v>32</v>
       </c>
       <c r="B112" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="C112" t="s">
+        <v>38</v>
       </c>
       <c r="D112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E112" t="s">
-        <v>207</v>
+        <v>132</v>
       </c>
       <c r="G112" t="s">
-        <v>210</v>
+        <v>138</v>
       </c>
       <c r="H112" s="1">
-        <v>46093</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B113" t="s">
-        <v>23</v>
-      </c>
-      <c r="C113" t="s">
-        <v>127</v>
+        <v>94</v>
+      </c>
+      <c r="C113">
+        <v>200</v>
       </c>
       <c r="D113" t="s">
         <v>13</v>
       </c>
       <c r="E113" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="F113" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="G113" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H113" s="1">
-        <v>46093</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B114" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="D114" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E114" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F114" t="s">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="G114" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="H114" s="1">
-        <v>46093</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="B115" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C115" t="s">
+        <v>42</v>
       </c>
       <c r="D115" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E115" t="s">
-        <v>30</v>
-      </c>
-      <c r="F115" t="s">
-        <v>203</v>
+        <v>45</v>
       </c>
       <c r="G115" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H115" s="1">
-        <v>46093</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c r="B116" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C116" t="s">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="D116" t="s">
         <v>14</v>
       </c>
       <c r="E116" t="s">
-        <v>81</v>
-      </c>
-      <c r="F116" t="s">
-        <v>204</v>
+        <v>43</v>
       </c>
       <c r="G116" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="H116" s="1">
-        <v>46093</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="B117" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C117" t="s">
-        <v>37</v>
-      </c>
-      <c r="D117" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E117" t="s">
-        <v>53</v>
+        <v>57</v>
+      </c>
+      <c r="F117" t="s">
+        <v>157</v>
       </c>
       <c r="G117" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H117" s="1">
-        <v>46093</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c r="B118" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="C118" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="D118" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E118" t="s">
-        <v>39</v>
+        <v>65</v>
+      </c>
+      <c r="F118" t="s">
+        <v>159</v>
       </c>
       <c r="G118" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="H118" s="1">
-        <v>46089</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>173</v>
+        <v>32</v>
       </c>
       <c r="B119" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="C119" t="s">
+        <v>33</v>
       </c>
       <c r="D119" t="s">
         <v>14</v>
       </c>
-      <c r="E119">
-        <v>23616</v>
-      </c>
-      <c r="F119" t="s">
-        <v>212</v>
-      </c>
-      <c r="G119">
-        <v>23616</v>
+      <c r="E119" t="s">
+        <v>81</v>
+      </c>
+      <c r="G119" t="s">
+        <v>82</v>
       </c>
       <c r="H119" s="1">
-        <v>46089</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>170</v>
+        <v>47</v>
       </c>
       <c r="B120" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C120" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D120" t="s">
         <v>14</v>
       </c>
       <c r="E120" t="s">
-        <v>34</v>
+        <v>53</v>
+      </c>
+      <c r="F120" t="s">
+        <v>160</v>
       </c>
       <c r="G120" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H120" s="1">
-        <v>46089</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B121" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="C121" t="s">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="D121" t="s">
         <v>14</v>
       </c>
       <c r="E121" t="s">
-        <v>207</v>
+        <v>197</v>
+      </c>
+      <c r="F121" t="s">
+        <v>193</v>
       </c>
       <c r="G121" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="H121" s="1">
-        <v>46089</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="D122" t="s">
         <v>13</v>
       </c>
       <c r="E122" t="s">
-        <v>213</v>
+        <v>195</v>
+      </c>
+      <c r="F122" t="s">
+        <v>194</v>
       </c>
       <c r="G122" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="H122" s="1">
-        <v>46089</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>5</v>
+        <v>62</v>
+      </c>
+      <c r="C123" t="s">
+        <v>24</v>
       </c>
       <c r="D123" t="s">
         <v>14</v>
       </c>
       <c r="E123" t="s">
-        <v>214</v>
+        <v>57</v>
       </c>
       <c r="G123" t="s">
-        <v>216</v>
+        <v>58</v>
       </c>
       <c r="H123" s="1">
-        <v>46089</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B124" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E124" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G124" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H124" s="1">
-        <v>46089</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="B125" t="s">
         <v>5</v>
       </c>
-      <c r="C125" t="s">
-        <v>96</v>
-      </c>
       <c r="D125" t="s">
         <v>14</v>
       </c>
       <c r="E125" t="s">
-        <v>98</v>
-      </c>
-      <c r="F125" t="s">
-        <v>175</v>
+        <v>45</v>
       </c>
       <c r="G125" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="H125" s="1">
-        <v>46089</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B126" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D126" t="s">
         <v>14</v>
       </c>
       <c r="E126" t="s">
-        <v>222</v>
+        <v>43</v>
       </c>
       <c r="G126" t="s">
-        <v>227</v>
+        <v>44</v>
       </c>
       <c r="H126" s="1">
-        <v>46085</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c r="B127" t="s">
         <v>3</v>
       </c>
+      <c r="C127" t="s">
+        <v>26</v>
+      </c>
       <c r="D127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E127" t="s">
-        <v>217</v>
+        <v>31</v>
+      </c>
+      <c r="F127" t="s">
+        <v>234</v>
       </c>
       <c r="G127" t="s">
-        <v>233</v>
+        <v>30</v>
       </c>
       <c r="H127" s="1">
-        <v>46085</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>171</v>
+        <v>25</v>
+      </c>
+      <c r="B128" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" t="s">
+        <v>13</v>
       </c>
       <c r="E128" t="s">
-        <v>221</v>
+        <v>71</v>
+      </c>
+      <c r="F128" t="s">
+        <v>240</v>
       </c>
       <c r="G128" t="s">
-        <v>226</v>
+        <v>72</v>
       </c>
       <c r="H128" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>211</v>
+        <v>32</v>
       </c>
       <c r="B129" t="s">
         <v>5</v>
       </c>
       <c r="C129" t="s">
-        <v>96</v>
+        <v>233</v>
       </c>
       <c r="D129" t="s">
-        <v>14</v>
+        <v>242</v>
       </c>
       <c r="E129" t="s">
-        <v>98</v>
+        <v>110</v>
+      </c>
+      <c r="F129" t="s">
+        <v>240</v>
       </c>
       <c r="G129" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="H129" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="B130" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C130" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E130" t="s">
-        <v>222</v>
+        <v>132</v>
+      </c>
+      <c r="F130" t="s">
+        <v>237</v>
       </c>
       <c r="G130" t="s">
-        <v>227</v>
+        <v>138</v>
       </c>
       <c r="H130" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>170</v>
+        <v>22</v>
       </c>
       <c r="B131" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C131" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="D131" t="s">
         <v>14</v>
       </c>
       <c r="E131" t="s">
-        <v>223</v>
+        <v>57</v>
       </c>
       <c r="G131" t="s">
-        <v>228</v>
+        <v>58</v>
       </c>
       <c r="H131" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>194</v>
+        <v>29</v>
       </c>
       <c r="B132" t="s">
-        <v>2</v>
+        <v>63</v>
+      </c>
+      <c r="C132" t="s">
+        <v>64</v>
       </c>
       <c r="D132" t="s">
         <v>14</v>
       </c>
       <c r="E132" t="s">
-        <v>81</v>
+        <v>65</v>
+      </c>
+      <c r="F132" t="s">
+        <v>239</v>
       </c>
       <c r="G132" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="H132" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="B133" t="s">
         <v>2</v>
@@ -4308,21 +4317,21 @@
         <v>14</v>
       </c>
       <c r="E133" t="s">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="F133" t="s">
-        <v>195</v>
+        <v>236</v>
       </c>
       <c r="G133" t="s">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="H133" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="B134" t="s">
         <v>6</v>
@@ -4334,321 +4343,334 @@
         <v>13</v>
       </c>
       <c r="E134" t="s">
-        <v>39</v>
+        <v>235</v>
+      </c>
+      <c r="F134" t="s">
+        <v>238</v>
       </c>
       <c r="G134" t="s">
-        <v>40</v>
+        <v>241</v>
       </c>
       <c r="H134" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>170</v>
+        <v>36</v>
       </c>
       <c r="B135" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C135" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D135" t="s">
         <v>14</v>
       </c>
       <c r="E135" t="s">
-        <v>34</v>
-      </c>
-      <c r="F135" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G135" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H135" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="B136" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C136" t="s">
-        <v>219</v>
+        <v>229</v>
+      </c>
+      <c r="D136" t="s">
+        <v>13</v>
       </c>
       <c r="E136" t="s">
-        <v>225</v>
+        <v>31</v>
       </c>
       <c r="F136" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="G136" t="s">
-        <v>230</v>
+        <v>30</v>
       </c>
       <c r="H136" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>173</v>
+        <v>32</v>
       </c>
       <c r="B137" t="s">
+        <v>63</v>
+      </c>
+      <c r="C137" t="s">
+        <v>64</v>
+      </c>
+      <c r="D137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E137" t="s">
+        <v>249</v>
+      </c>
+      <c r="G137" t="s">
+        <v>256</v>
+      </c>
+      <c r="H137" s="1">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>32</v>
+      </c>
+      <c r="B138" t="s">
         <v>5</v>
       </c>
-      <c r="C137" t="s">
-        <v>74</v>
-      </c>
-      <c r="D137" t="s">
-        <v>14</v>
-      </c>
-      <c r="E137" t="s">
-        <v>45</v>
-      </c>
-      <c r="G137" t="s">
-        <v>46</v>
-      </c>
-      <c r="H137" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
-        <v>169</v>
-      </c>
-      <c r="B138" t="s">
-        <v>3</v>
-      </c>
       <c r="C138" t="s">
-        <v>26</v>
+        <v>233</v>
       </c>
       <c r="D138" t="s">
-        <v>13</v>
+        <v>242</v>
       </c>
       <c r="E138" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="G138" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="H138" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="B139" t="s">
         <v>6</v>
       </c>
       <c r="C139" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D139" t="s">
         <v>13</v>
       </c>
       <c r="E139" t="s">
-        <v>56</v>
+        <v>271</v>
+      </c>
+      <c r="F139" t="s">
+        <v>157</v>
       </c>
       <c r="G139" t="s">
-        <v>41</v>
+        <v>274</v>
       </c>
       <c r="H139" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>202</v>
+        <v>32</v>
       </c>
       <c r="B140" t="s">
-        <v>3</v>
+        <v>261</v>
+      </c>
+      <c r="C140" t="s">
+        <v>245</v>
       </c>
       <c r="D140" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E140" t="s">
-        <v>28</v>
+        <v>253</v>
+      </c>
+      <c r="F140" t="s">
+        <v>184</v>
       </c>
       <c r="G140" t="s">
-        <v>27</v>
+        <v>258</v>
       </c>
       <c r="H140" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>173</v>
+        <v>32</v>
       </c>
       <c r="B141" t="s">
+        <v>4</v>
+      </c>
+      <c r="C141" t="s">
+        <v>144</v>
+      </c>
+      <c r="D141" t="s">
+        <v>13</v>
+      </c>
+      <c r="E141" t="s">
+        <v>277</v>
+      </c>
+      <c r="G141" t="s">
+        <v>276</v>
+      </c>
+      <c r="H141" s="1">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B142" t="s">
+        <v>264</v>
+      </c>
+      <c r="C142" t="s">
+        <v>263</v>
+      </c>
+      <c r="D142" t="s">
+        <v>13</v>
+      </c>
+      <c r="E142" t="s">
+        <v>272</v>
+      </c>
+      <c r="F142" t="s">
+        <v>157</v>
+      </c>
+      <c r="G142" t="s">
+        <v>275</v>
+      </c>
+      <c r="H142" s="1">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>29</v>
+      </c>
+      <c r="B143" t="s">
         <v>5</v>
       </c>
-      <c r="D141" t="s">
-        <v>14</v>
-      </c>
-      <c r="E141" t="s">
-        <v>218</v>
-      </c>
-      <c r="G141" t="s">
-        <v>234</v>
-      </c>
-      <c r="H141" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
-        <v>8</v>
-      </c>
-      <c r="B142" t="s">
-        <v>2</v>
-      </c>
-      <c r="C142" t="s">
-        <v>33</v>
-      </c>
-      <c r="D142" t="s">
-        <v>14</v>
-      </c>
-      <c r="E142" t="s">
+      <c r="C143" t="s">
+        <v>145</v>
+      </c>
+      <c r="D143" t="s">
+        <v>14</v>
+      </c>
+      <c r="E143" t="s">
+        <v>43</v>
+      </c>
+      <c r="G143" t="s">
+        <v>44</v>
+      </c>
+      <c r="H143" s="1">
+        <v>46099</v>
+      </c>
+      <c r="L143" s="2"/>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>243</v>
+      </c>
+      <c r="B144" t="s">
+        <v>23</v>
+      </c>
+      <c r="C144" t="s">
+        <v>262</v>
+      </c>
+      <c r="D144" t="s">
+        <v>265</v>
+      </c>
+      <c r="E144" t="s">
+        <v>269</v>
+      </c>
+      <c r="F144" t="s">
+        <v>108</v>
+      </c>
+      <c r="G144" t="s">
+        <v>278</v>
+      </c>
+      <c r="H144" s="1">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
         <v>231</v>
       </c>
-      <c r="G142" t="s">
+      <c r="B145" t="s">
         <v>232</v>
       </c>
-      <c r="H142" s="1">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>22</v>
-      </c>
-      <c r="B143" t="s">
-        <v>23</v>
-      </c>
-      <c r="C143" t="s">
-        <v>24</v>
-      </c>
-      <c r="D143" t="s">
-        <v>14</v>
-      </c>
-      <c r="E143" t="s">
-        <v>57</v>
-      </c>
-      <c r="G143" t="s">
-        <v>58</v>
-      </c>
-      <c r="H143" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>36</v>
-      </c>
-      <c r="B144" t="s">
-        <v>3</v>
-      </c>
-      <c r="C144" t="s">
-        <v>37</v>
-      </c>
-      <c r="D144" t="s">
-        <v>14</v>
-      </c>
-      <c r="E144" t="s">
-        <v>53</v>
-      </c>
-      <c r="G144" t="s">
-        <v>55</v>
-      </c>
-      <c r="H144" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
-        <v>29</v>
-      </c>
-      <c r="B145" t="s">
-        <v>3</v>
-      </c>
       <c r="C145" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D145" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E145" t="s">
-        <v>31</v>
-      </c>
-      <c r="F145" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="G145" t="s">
-        <v>30</v>
+        <v>273</v>
       </c>
       <c r="H145" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>32</v>
       </c>
       <c r="B146" t="s">
-        <v>2</v>
+        <v>246</v>
       </c>
       <c r="C146" t="s">
-        <v>33</v>
+        <v>247</v>
       </c>
       <c r="D146" t="s">
         <v>14</v>
       </c>
       <c r="E146" t="s">
-        <v>81</v>
-      </c>
-      <c r="F146" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="G146" t="s">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="H146" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>32</v>
       </c>
       <c r="B147" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C147" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D147" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E147" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="F147" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="G147" t="s">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="H147" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>32</v>
       </c>
@@ -4656,322 +4678,318 @@
         <v>6</v>
       </c>
       <c r="C148" t="s">
-        <v>38</v>
+        <v>230</v>
       </c>
       <c r="D148" t="s">
         <v>13</v>
       </c>
       <c r="E148" t="s">
+        <v>235</v>
+      </c>
+      <c r="F148" t="s">
+        <v>268</v>
+      </c>
+      <c r="G148" t="s">
         <v>241</v>
       </c>
-      <c r="F148" t="s">
-        <v>244</v>
-      </c>
-      <c r="G148" t="s">
-        <v>247</v>
-      </c>
       <c r="H148" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B149" t="s">
         <v>63</v>
       </c>
       <c r="C149" t="s">
-        <v>64</v>
+        <v>266</v>
       </c>
       <c r="D149" t="s">
         <v>14</v>
       </c>
       <c r="E149" t="s">
-        <v>65</v>
-      </c>
-      <c r="F149" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="G149" t="s">
-        <v>66</v>
+        <v>257</v>
       </c>
       <c r="H149" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B150" t="s">
         <v>3</v>
       </c>
+      <c r="C150" t="s">
+        <v>26</v>
+      </c>
       <c r="D150" t="s">
         <v>13</v>
       </c>
       <c r="E150" t="s">
-        <v>71</v>
-      </c>
-      <c r="F150" t="s">
-        <v>246</v>
+        <v>31</v>
       </c>
       <c r="G150" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H150" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>32</v>
       </c>
       <c r="B151" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="C151" t="s">
-        <v>239</v>
+        <v>33</v>
       </c>
       <c r="D151" t="s">
-        <v>248</v>
+        <v>14</v>
       </c>
       <c r="E151" t="s">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="F151" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="G151" t="s">
-        <v>118</v>
+        <v>260</v>
       </c>
       <c r="H151" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B152" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="C152" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D152" t="s">
         <v>14</v>
       </c>
       <c r="E152" t="s">
-        <v>57</v>
+        <v>249</v>
+      </c>
+      <c r="F152" t="s">
+        <v>129</v>
       </c>
       <c r="G152" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="H152" s="1">
         <v>46100</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B153" t="s">
-        <v>3</v>
+        <v>244</v>
       </c>
       <c r="C153" t="s">
-        <v>26</v>
+        <v>245</v>
       </c>
       <c r="D153" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>31</v>
+        <v>253</v>
       </c>
       <c r="G153" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
       <c r="H153" s="1">
         <v>46100</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B154" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C154" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D154" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E154" t="s">
-        <v>43</v>
-      </c>
-      <c r="F154" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="G154" t="s">
-        <v>44</v>
+        <v>276</v>
       </c>
       <c r="H154" s="1">
         <v>46100</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B155" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="C155" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="D155" t="s">
         <v>14</v>
       </c>
       <c r="E155" t="s">
-        <v>255</v>
+        <v>43</v>
       </c>
       <c r="F155" t="s">
-        <v>129</v>
+        <v>248</v>
       </c>
       <c r="G155" t="s">
-        <v>262</v>
+        <v>44</v>
       </c>
       <c r="H155" s="1">
         <v>46100</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B156" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C156" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D156" t="s">
         <v>14</v>
       </c>
       <c r="E156" t="s">
-        <v>81</v>
-      </c>
-      <c r="F156" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="G156" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="H156" s="1">
         <v>46100</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B157" t="s">
         <v>63</v>
       </c>
       <c r="C157" t="s">
-        <v>257</v>
+        <v>64</v>
       </c>
       <c r="D157" t="s">
         <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>258</v>
+        <v>65</v>
       </c>
       <c r="G157" t="s">
-        <v>263</v>
+        <v>66</v>
       </c>
       <c r="H157" s="1">
         <v>46100</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>32</v>
       </c>
       <c r="B158" t="s">
-        <v>6</v>
+        <v>246</v>
       </c>
       <c r="C158" t="s">
-        <v>38</v>
+        <v>247</v>
       </c>
       <c r="D158" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E158" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="G158" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="H158" s="1">
         <v>46100</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B159" t="s">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="C159" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D159" t="s">
         <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>65</v>
+        <v>81</v>
+      </c>
+      <c r="F159" t="s">
+        <v>250</v>
       </c>
       <c r="G159" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H159" s="1">
         <v>46100</v>
       </c>
-      <c r="L159" s="2"/>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>249</v>
+        <v>32</v>
       </c>
       <c r="B160" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C160" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="D160" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E160" t="s">
-        <v>53</v>
+        <v>235</v>
       </c>
       <c r="G160" t="s">
-        <v>55</v>
+        <v>241</v>
       </c>
       <c r="H160" s="1">
         <v>46100</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>32</v>
       </c>
       <c r="B161" t="s">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="C161" t="s">
         <v>251</v>
@@ -4980,455 +4998,53 @@
         <v>14</v>
       </c>
       <c r="E161" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="G161" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="H161" s="1">
         <v>46100</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>32</v>
+        <v>243</v>
       </c>
       <c r="B162" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C162" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="D162" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E162" t="s">
-        <v>283</v>
+        <v>53</v>
       </c>
       <c r="G162" t="s">
-        <v>282</v>
+        <v>55</v>
       </c>
       <c r="H162" s="1">
         <v>46100</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A163" t="s">
-        <v>32</v>
-      </c>
-      <c r="B163" t="s">
-        <v>252</v>
-      </c>
-      <c r="C163" t="s">
-        <v>253</v>
-      </c>
-      <c r="D163" t="s">
-        <v>14</v>
-      </c>
-      <c r="E163" t="s">
-        <v>260</v>
-      </c>
-      <c r="G163" t="s">
-        <v>265</v>
-      </c>
-      <c r="H163" s="1">
-        <v>46100</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A164" t="s">
-        <v>32</v>
-      </c>
-      <c r="B164" t="s">
-        <v>92</v>
-      </c>
-      <c r="C164" t="s">
-        <v>33</v>
-      </c>
-      <c r="D164" t="s">
-        <v>14</v>
-      </c>
-      <c r="E164" t="s">
-        <v>261</v>
-      </c>
-      <c r="F164" t="s">
-        <v>276</v>
-      </c>
-      <c r="G164" t="s">
-        <v>266</v>
-      </c>
-      <c r="H164" s="1">
-        <v>46100</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
-        <v>29</v>
-      </c>
-      <c r="B165" t="s">
-        <v>3</v>
-      </c>
-      <c r="C165" t="s">
-        <v>235</v>
-      </c>
-      <c r="D165" t="s">
-        <v>13</v>
-      </c>
-      <c r="E165" t="s">
-        <v>31</v>
-      </c>
-      <c r="F165" t="s">
-        <v>176</v>
-      </c>
-      <c r="G165" t="s">
-        <v>30</v>
-      </c>
-      <c r="H165" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A166" t="s">
-        <v>32</v>
-      </c>
-      <c r="B166" t="s">
-        <v>6</v>
-      </c>
-      <c r="C166" t="s">
-        <v>236</v>
-      </c>
-      <c r="D166" t="s">
-        <v>13</v>
-      </c>
-      <c r="E166" t="s">
-        <v>241</v>
-      </c>
-      <c r="F166" t="s">
-        <v>274</v>
-      </c>
-      <c r="G166" t="s">
-        <v>247</v>
-      </c>
-      <c r="H166" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A167" t="s">
-        <v>32</v>
-      </c>
-      <c r="B167" t="s">
-        <v>4</v>
-      </c>
-      <c r="C167" t="s">
-        <v>144</v>
-      </c>
-      <c r="D167" t="s">
-        <v>13</v>
-      </c>
-      <c r="E167" t="s">
-        <v>283</v>
-      </c>
-      <c r="G167" t="s">
-        <v>282</v>
-      </c>
-      <c r="H167" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A168" t="s">
-        <v>237</v>
-      </c>
-      <c r="B168" t="s">
-        <v>238</v>
-      </c>
-      <c r="C168" t="s">
-        <v>14</v>
-      </c>
-      <c r="D168" t="s">
-        <v>14</v>
-      </c>
-      <c r="E168" t="s">
-        <v>273</v>
-      </c>
-      <c r="G168" t="s">
-        <v>279</v>
-      </c>
-      <c r="H168" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A169" t="s">
-        <v>32</v>
-      </c>
-      <c r="B169" t="s">
-        <v>267</v>
-      </c>
-      <c r="C169" t="s">
-        <v>251</v>
-      </c>
-      <c r="D169" t="s">
-        <v>14</v>
-      </c>
-      <c r="E169" t="s">
-        <v>259</v>
-      </c>
-      <c r="F169" t="s">
-        <v>186</v>
-      </c>
-      <c r="G169" t="s">
-        <v>264</v>
-      </c>
-      <c r="H169" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A170" t="s">
-        <v>29</v>
-      </c>
-      <c r="B170" t="s">
-        <v>5</v>
-      </c>
-      <c r="C170" t="s">
-        <v>146</v>
-      </c>
-      <c r="D170" t="s">
-        <v>14</v>
-      </c>
-      <c r="E170" t="s">
-        <v>43</v>
-      </c>
-      <c r="G170" t="s">
-        <v>44</v>
-      </c>
-      <c r="H170" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A171" t="s">
-        <v>32</v>
-      </c>
-      <c r="B171" t="s">
-        <v>2</v>
-      </c>
-      <c r="C171" t="s">
-        <v>33</v>
-      </c>
-      <c r="D171" t="s">
-        <v>14</v>
-      </c>
-      <c r="E171" t="s">
-        <v>81</v>
-      </c>
-      <c r="F171" t="s">
-        <v>238</v>
-      </c>
-      <c r="G171" t="s">
-        <v>82</v>
-      </c>
-      <c r="H171" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A172" t="s">
-        <v>32</v>
-      </c>
-      <c r="B172" t="s">
-        <v>5</v>
-      </c>
-      <c r="C172" t="s">
-        <v>239</v>
-      </c>
-      <c r="D172" t="s">
-        <v>248</v>
-      </c>
-      <c r="E172" t="s">
-        <v>110</v>
-      </c>
-      <c r="G172" t="s">
-        <v>118</v>
-      </c>
-      <c r="H172" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A173" t="s">
-        <v>249</v>
-      </c>
-      <c r="B173" t="s">
-        <v>23</v>
-      </c>
-      <c r="C173" t="s">
-        <v>268</v>
-      </c>
-      <c r="D173" t="s">
-        <v>271</v>
-      </c>
-      <c r="E173" t="s">
-        <v>275</v>
-      </c>
-      <c r="F173" t="s">
-        <v>108</v>
-      </c>
-      <c r="G173" t="s">
-        <v>284</v>
-      </c>
-      <c r="H173" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A174" t="s">
-        <v>32</v>
-      </c>
-      <c r="B174" t="s">
-        <v>63</v>
-      </c>
-      <c r="C174" t="s">
-        <v>64</v>
-      </c>
-      <c r="D174" t="s">
-        <v>14</v>
-      </c>
-      <c r="E174" t="s">
-        <v>255</v>
-      </c>
-      <c r="G174" t="s">
-        <v>262</v>
-      </c>
-      <c r="H174" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A175" t="s">
-        <v>32</v>
-      </c>
-      <c r="B175" t="s">
-        <v>252</v>
-      </c>
-      <c r="C175" t="s">
-        <v>253</v>
-      </c>
-      <c r="D175" t="s">
-        <v>14</v>
-      </c>
-      <c r="E175" t="s">
-        <v>260</v>
-      </c>
-      <c r="G175" t="s">
-        <v>265</v>
-      </c>
-      <c r="H175" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A176" t="s">
-        <v>32</v>
-      </c>
-      <c r="B176" t="s">
-        <v>63</v>
-      </c>
-      <c r="C176" t="s">
-        <v>272</v>
-      </c>
-      <c r="D176" t="s">
-        <v>14</v>
-      </c>
-      <c r="E176" t="s">
-        <v>258</v>
-      </c>
-      <c r="G176" t="s">
-        <v>263</v>
-      </c>
-      <c r="H176" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A177" t="s">
-        <v>32</v>
-      </c>
-      <c r="B177" t="s">
-        <v>6</v>
-      </c>
-      <c r="C177" t="s">
-        <v>11</v>
-      </c>
-      <c r="D177" t="s">
-        <v>13</v>
-      </c>
-      <c r="E177" t="s">
-        <v>277</v>
-      </c>
-      <c r="F177" t="s">
-        <v>159</v>
-      </c>
-      <c r="G177" t="s">
-        <v>280</v>
-      </c>
-      <c r="H177" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B178" t="s">
-        <v>270</v>
-      </c>
-      <c r="C178" t="s">
-        <v>269</v>
-      </c>
-      <c r="D178" t="s">
-        <v>13</v>
-      </c>
-      <c r="E178" t="s">
-        <v>278</v>
-      </c>
-      <c r="F178" t="s">
-        <v>159</v>
-      </c>
-      <c r="G178" t="s">
-        <v>281</v>
-      </c>
-      <c r="H178" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A179" t="s">
-        <v>170</v>
-      </c>
-      <c r="B179" t="s">
-        <v>63</v>
-      </c>
-      <c r="D179" t="s">
-        <v>14</v>
-      </c>
-      <c r="E179" t="s">
-        <v>255</v>
-      </c>
-      <c r="G179" t="s">
-        <v>262</v>
-      </c>
-      <c r="H179" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J185" s="2"/>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J187" s="2"/>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H163" s="1"/>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J169" s="2"/>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J171" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J141" xr:uid="{8FC0DC25-20B3-834F-98DA-243C4E7C4E30}"/>
+  <autoFilter ref="A1:J163" xr:uid="{8FC0DC25-20B3-834F-98DA-243C4E7C4E30}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J163">
+      <sortCondition ref="H1:H163"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/vehicles.xlsx
+++ b/vehicles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandyeyster/Sandys documents/GEO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE0C229-0E16-BF47-A7C9-E0BC8C0A1F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F018A79-F4D7-E44B-A005-3BF40C5B456F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2440" yWindow="760" windowWidth="28660" windowHeight="20100" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="325">
   <si>
     <t>Color</t>
   </si>
@@ -966,6 +966,54 @@
   </si>
   <si>
     <t>MD2AT2272</t>
+  </si>
+  <si>
+    <t>DC8362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Black</t>
+  </si>
+  <si>
+    <t>NJ L18KVY</t>
+  </si>
+  <si>
+    <t>VA TFL2108</t>
+  </si>
+  <si>
+    <t>Beige</t>
+  </si>
+  <si>
+    <t>BLack</t>
+  </si>
+  <si>
+    <t>NJ U72RZF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Fe </t>
+  </si>
+  <si>
+    <t>DC 15779</t>
+  </si>
+  <si>
+    <t>NY HHB8528</t>
+  </si>
+  <si>
+    <t>NJL18KVY</t>
+  </si>
+  <si>
+    <t>VATFL2108</t>
+  </si>
+  <si>
+    <t>NJU72RZF</t>
+  </si>
+  <si>
+    <t>NYHHB8528</t>
+  </si>
+  <si>
+    <t>DC15779</t>
   </si>
 </sst>
 </file>
@@ -1008,13 +1056,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1349,8 +1395,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC0DC25-20B3-834F-98DA-243C4E7C4E30}">
-  <dimension ref="A1:L210"/>
+  <dimension ref="A1:P226"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
@@ -5760,481 +5810,849 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="190" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="4" t="s">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
         <v>166</v>
       </c>
-      <c r="B190" s="4" t="s">
+      <c r="B190" t="s">
         <v>239</v>
       </c>
-      <c r="D190" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E190" s="4" t="s">
+      <c r="D190" t="s">
+        <v>14</v>
+      </c>
+      <c r="E190" t="s">
         <v>294</v>
       </c>
-      <c r="F190" s="4" t="s">
+      <c r="F190" t="s">
         <v>190</v>
       </c>
-      <c r="G190" s="4" t="s">
+      <c r="G190" t="s">
         <v>302</v>
       </c>
-      <c r="H190" s="5">
+      <c r="H190" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="191" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B191" s="4" t="s">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>32</v>
+      </c>
+      <c r="B191" t="s">
         <v>2</v>
       </c>
-      <c r="C191" s="4" t="s">
+      <c r="C191" t="s">
         <v>33</v>
       </c>
-      <c r="D191" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E191" s="4" t="s">
+      <c r="D191" t="s">
+        <v>14</v>
+      </c>
+      <c r="E191" t="s">
         <v>80</v>
       </c>
-      <c r="F191" s="4" t="s">
+      <c r="F191" t="s">
         <v>227</v>
       </c>
-      <c r="G191" s="4" t="s">
+      <c r="G191" t="s">
         <v>81</v>
       </c>
-      <c r="H191" s="5">
+      <c r="H191" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="192" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="4" t="s">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
         <v>166</v>
       </c>
-      <c r="B192" s="4" t="s">
+      <c r="B192" t="s">
         <v>241</v>
       </c>
-      <c r="E192" s="4" t="s">
+      <c r="E192" t="s">
         <v>249</v>
       </c>
-      <c r="G192" s="4" t="s">
+      <c r="G192" t="s">
         <v>254</v>
       </c>
-      <c r="H192" s="5">
+      <c r="H192" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="193" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="4" t="s">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
         <v>29</v>
       </c>
-      <c r="B193" s="4" t="s">
+      <c r="B193" t="s">
         <v>3</v>
       </c>
-      <c r="E193" s="4" t="s">
+      <c r="E193" t="s">
         <v>295</v>
       </c>
-      <c r="G193" s="4" t="s">
+      <c r="G193" t="s">
         <v>303</v>
       </c>
-      <c r="H193" s="5">
+      <c r="H193" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="194" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="4" t="s">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
         <v>166</v>
       </c>
-      <c r="B194" s="4" t="s">
+      <c r="B194" t="s">
         <v>2</v>
       </c>
-      <c r="C194" s="4" t="s">
+      <c r="C194" t="s">
         <v>33</v>
       </c>
-      <c r="D194" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E194" s="4" t="s">
+      <c r="D194" t="s">
+        <v>14</v>
+      </c>
+      <c r="E194" t="s">
         <v>250</v>
       </c>
-      <c r="G194" s="4" t="s">
+      <c r="G194" t="s">
         <v>255</v>
       </c>
-      <c r="H194" s="5">
+      <c r="H194" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="195" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="4" t="s">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
         <v>29</v>
       </c>
-      <c r="B195" s="4" t="s">
+      <c r="B195" t="s">
         <v>3</v>
       </c>
-      <c r="C195" s="4" t="s">
+      <c r="C195" t="s">
         <v>87</v>
       </c>
-      <c r="D195" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E195" s="4" t="s">
+      <c r="D195" t="s">
+        <v>14</v>
+      </c>
+      <c r="E195" t="s">
         <v>272</v>
       </c>
-      <c r="F195" s="4" t="s">
+      <c r="F195" t="s">
         <v>299</v>
       </c>
-      <c r="G195" s="4" t="s">
+      <c r="G195" t="s">
         <v>273</v>
       </c>
-      <c r="H195" s="5">
+      <c r="H195" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="196" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="4" t="s">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
         <v>29</v>
       </c>
-      <c r="B196" s="4" t="s">
+      <c r="B196" t="s">
         <v>3</v>
       </c>
-      <c r="C196" s="4" t="s">
+      <c r="C196" t="s">
         <v>87</v>
       </c>
-      <c r="D196" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E196" s="4">
+      <c r="D196" t="s">
+        <v>14</v>
+      </c>
+      <c r="E196">
         <v>23616</v>
       </c>
-      <c r="F196" s="4" t="s">
+      <c r="F196" t="s">
         <v>300</v>
       </c>
-      <c r="G196" s="4">
+      <c r="G196">
         <v>23616</v>
       </c>
-      <c r="H196" s="5">
+      <c r="H196" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="197" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="4" t="s">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
         <v>29</v>
       </c>
-      <c r="B197" s="4" t="s">
+      <c r="B197" t="s">
         <v>143</v>
       </c>
-      <c r="C197" s="4" t="s">
+      <c r="C197" t="s">
         <v>274</v>
       </c>
-      <c r="D197" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E197" s="4" t="s">
+      <c r="D197" t="s">
+        <v>13</v>
+      </c>
+      <c r="E197" t="s">
         <v>198</v>
       </c>
-      <c r="G197" s="4" t="s">
+      <c r="G197" t="s">
         <v>200</v>
       </c>
-      <c r="H197" s="5">
+      <c r="H197" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="198" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="4" t="s">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
         <v>29</v>
       </c>
-      <c r="B198" s="4" t="s">
+      <c r="B198" t="s">
         <v>5</v>
       </c>
-      <c r="C198" s="4" t="s">
+      <c r="C198" t="s">
         <v>144</v>
       </c>
-      <c r="D198" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E198" s="4" t="s">
+      <c r="D198" t="s">
+        <v>14</v>
+      </c>
+      <c r="E198" t="s">
         <v>43</v>
       </c>
-      <c r="F198" s="4" t="s">
+      <c r="F198" t="s">
         <v>243</v>
       </c>
-      <c r="G198" s="4" t="s">
+      <c r="G198" t="s">
         <v>44</v>
       </c>
-      <c r="H198" s="5">
+      <c r="H198" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="199" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B199" s="4" t="s">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>32</v>
+      </c>
+      <c r="B199" t="s">
         <v>6</v>
       </c>
-      <c r="C199" s="4" t="s">
+      <c r="C199" t="s">
         <v>38</v>
       </c>
-      <c r="D199" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E199" s="4" t="s">
+      <c r="D199" t="s">
+        <v>13</v>
+      </c>
+      <c r="E199" t="s">
         <v>230</v>
       </c>
-      <c r="G199" s="4" t="s">
+      <c r="G199" t="s">
         <v>236</v>
       </c>
-      <c r="H199" s="5">
+      <c r="H199" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="200" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B200" s="4" t="s">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>32</v>
+      </c>
+      <c r="B200" t="s">
         <v>63</v>
       </c>
-      <c r="C200" s="4" t="s">
+      <c r="C200" t="s">
         <v>275</v>
       </c>
-      <c r="D200" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E200" s="4" t="s">
+      <c r="D200" t="s">
+        <v>14</v>
+      </c>
+      <c r="E200" t="s">
         <v>278</v>
       </c>
-      <c r="G200" s="4" t="s">
+      <c r="G200" t="s">
         <v>283</v>
       </c>
-      <c r="H200" s="5">
+      <c r="H200" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="201" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B201" s="4" t="s">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>32</v>
+      </c>
+      <c r="B201" t="s">
         <v>239</v>
       </c>
-      <c r="D201" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E201" s="4" t="s">
+      <c r="D201" t="s">
+        <v>14</v>
+      </c>
+      <c r="E201" t="s">
         <v>248</v>
       </c>
-      <c r="G201" s="4" t="s">
+      <c r="G201" t="s">
         <v>253</v>
       </c>
-      <c r="H201" s="5">
+      <c r="H201" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="202" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B202" s="4" t="s">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>32</v>
+      </c>
+      <c r="B202" t="s">
         <v>23</v>
       </c>
-      <c r="C202" s="4" t="s">
+      <c r="C202" t="s">
         <v>188</v>
       </c>
-      <c r="D202" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E202" s="4" t="s">
+      <c r="D202" t="s">
+        <v>14</v>
+      </c>
+      <c r="E202" t="s">
         <v>280</v>
       </c>
-      <c r="G202" s="4" t="s">
+      <c r="G202" t="s">
         <v>285</v>
       </c>
-      <c r="H202" s="5">
+      <c r="H202" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="203" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B203" s="4" t="s">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>32</v>
+      </c>
+      <c r="B203" t="s">
         <v>63</v>
       </c>
-      <c r="C203" s="4" t="s">
+      <c r="C203" t="s">
         <v>64</v>
       </c>
-      <c r="D203" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E203" s="4" t="s">
+      <c r="D203" t="s">
+        <v>14</v>
+      </c>
+      <c r="E203" t="s">
         <v>296</v>
       </c>
-      <c r="G203" s="4" t="s">
+      <c r="G203" t="s">
         <v>304</v>
       </c>
-      <c r="H203" s="5">
+      <c r="H203" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="204" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B204" s="4" t="s">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>32</v>
+      </c>
+      <c r="B204" t="s">
         <v>4</v>
       </c>
-      <c r="C204" s="4" t="s">
+      <c r="C204" t="s">
         <v>143</v>
       </c>
-      <c r="D204" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E204" s="4" t="s">
+      <c r="D204" t="s">
+        <v>13</v>
+      </c>
+      <c r="E204" t="s">
         <v>270</v>
       </c>
-      <c r="G204" s="4" t="s">
+      <c r="G204" t="s">
         <v>269</v>
       </c>
-      <c r="H204" s="5">
+      <c r="H204" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="205" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B205" s="4" t="s">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>32</v>
+      </c>
+      <c r="B205" t="s">
         <v>63</v>
       </c>
-      <c r="C205" s="4" t="s">
+      <c r="C205" t="s">
         <v>246</v>
       </c>
-      <c r="D205" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E205" s="4" t="s">
+      <c r="D205" t="s">
+        <v>14</v>
+      </c>
+      <c r="E205" t="s">
         <v>247</v>
       </c>
-      <c r="G205" s="4" t="s">
+      <c r="G205" t="s">
         <v>252</v>
       </c>
-      <c r="H205" s="5">
+      <c r="H205" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="206" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="4" t="s">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
         <v>29</v>
       </c>
-      <c r="B206" s="4" t="s">
+      <c r="B206" t="s">
         <v>3</v>
       </c>
-      <c r="C206" s="4" t="s">
+      <c r="C206" t="s">
         <v>26</v>
       </c>
-      <c r="D206" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E206" s="4" t="s">
+      <c r="D206" t="s">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
         <v>31</v>
       </c>
-      <c r="G206" s="4" t="s">
+      <c r="G206" t="s">
         <v>30</v>
       </c>
-      <c r="H206" s="5">
+      <c r="H206" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="207" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="4" t="s">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
         <v>29</v>
       </c>
-      <c r="B207" s="4" t="s">
+      <c r="B207" t="s">
         <v>63</v>
       </c>
-      <c r="C207" s="4" t="s">
+      <c r="C207" t="s">
         <v>110</v>
       </c>
-      <c r="E207" s="4" t="s">
+      <c r="E207" t="s">
         <v>111</v>
       </c>
-      <c r="G207" s="4" t="s">
+      <c r="G207" t="s">
         <v>118</v>
       </c>
-      <c r="H207" s="5">
+      <c r="H207" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="208" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B208" s="4" t="s">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>32</v>
+      </c>
+      <c r="B208" t="s">
         <v>5</v>
       </c>
-      <c r="C208" s="4" t="s">
+      <c r="C208" t="s">
         <v>95</v>
       </c>
-      <c r="D208" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E208" s="4" t="s">
+      <c r="D208" t="s">
+        <v>14</v>
+      </c>
+      <c r="E208" t="s">
         <v>297</v>
       </c>
-      <c r="F208" s="4" t="s">
+      <c r="F208" t="s">
         <v>298</v>
       </c>
-      <c r="G208" s="4" t="s">
+      <c r="G208" t="s">
         <v>305</v>
       </c>
-      <c r="H208" s="5">
+      <c r="H208" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="209" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="4" t="s">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
         <v>22</v>
       </c>
-      <c r="B209" s="4" t="s">
+      <c r="B209" t="s">
         <v>2</v>
       </c>
-      <c r="D209" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E209" s="4" t="s">
+      <c r="D209" t="s">
+        <v>13</v>
+      </c>
+      <c r="E209" t="s">
         <v>301</v>
       </c>
-      <c r="G209" s="4" t="s">
+      <c r="G209" t="s">
         <v>306</v>
       </c>
-      <c r="H209" s="5">
+      <c r="H209" s="1">
         <v>46105</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A210" s="4" t="s">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
         <v>29</v>
       </c>
-      <c r="B210" s="4" t="s">
+      <c r="B210" t="s">
         <v>2</v>
       </c>
-      <c r="C210" s="4" t="s">
+      <c r="C210" t="s">
         <v>33</v>
       </c>
-      <c r="D210" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E210" s="4" t="s">
+      <c r="D210" t="s">
+        <v>14</v>
+      </c>
+      <c r="E210" t="s">
         <v>307</v>
       </c>
-      <c r="G210" s="4" t="s">
+      <c r="G210" t="s">
         <v>308</v>
       </c>
-      <c r="H210" s="5">
+      <c r="H210" s="1">
         <v>46105</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>310</v>
+      </c>
+      <c r="B211" t="s">
+        <v>2</v>
+      </c>
+      <c r="C211" t="s">
+        <v>33</v>
+      </c>
+      <c r="D211" t="s">
+        <v>14</v>
+      </c>
+      <c r="E211" t="s">
+        <v>312</v>
+      </c>
+      <c r="F211" t="s">
+        <v>54</v>
+      </c>
+      <c r="G211" t="s">
+        <v>320</v>
+      </c>
+      <c r="H211" s="1">
+        <v>46106</v>
+      </c>
+      <c r="P211" s="2"/>
+    </row>
+    <row r="212" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>311</v>
+      </c>
+      <c r="B212" t="s">
+        <v>2</v>
+      </c>
+      <c r="C212" t="s">
+        <v>33</v>
+      </c>
+      <c r="D212" t="s">
+        <v>14</v>
+      </c>
+      <c r="E212" t="s">
+        <v>80</v>
+      </c>
+      <c r="F212" t="s">
+        <v>227</v>
+      </c>
+      <c r="G212" t="s">
+        <v>81</v>
+      </c>
+      <c r="H212" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>311</v>
+      </c>
+      <c r="B213" t="s">
+        <v>63</v>
+      </c>
+      <c r="C213" t="s">
+        <v>64</v>
+      </c>
+      <c r="D213" t="s">
+        <v>14</v>
+      </c>
+      <c r="E213" t="s">
+        <v>296</v>
+      </c>
+      <c r="F213" t="s">
+        <v>128</v>
+      </c>
+      <c r="G213" t="s">
+        <v>304</v>
+      </c>
+      <c r="H213" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>32</v>
+      </c>
+      <c r="B214" t="s">
+        <v>241</v>
+      </c>
+      <c r="C214" t="s">
+        <v>242</v>
+      </c>
+      <c r="D214" t="s">
+        <v>14</v>
+      </c>
+      <c r="E214" t="s">
+        <v>313</v>
+      </c>
+      <c r="G214" t="s">
+        <v>321</v>
+      </c>
+      <c r="H214" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>29</v>
+      </c>
+      <c r="B215" t="s">
+        <v>143</v>
+      </c>
+      <c r="C215" t="s">
+        <v>274</v>
+      </c>
+      <c r="D215" t="s">
+        <v>13</v>
+      </c>
+      <c r="E215" t="s">
+        <v>198</v>
+      </c>
+      <c r="G215" t="s">
+        <v>200</v>
+      </c>
+      <c r="H215" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>32</v>
+      </c>
+      <c r="B216" t="s">
+        <v>6</v>
+      </c>
+      <c r="C216" t="s">
+        <v>38</v>
+      </c>
+      <c r="D216" t="s">
+        <v>13</v>
+      </c>
+      <c r="E216" t="s">
+        <v>230</v>
+      </c>
+      <c r="G216" t="s">
+        <v>236</v>
+      </c>
+      <c r="H216" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>314</v>
+      </c>
+      <c r="B217" t="s">
+        <v>3</v>
+      </c>
+      <c r="C217" t="s">
+        <v>26</v>
+      </c>
+      <c r="D217" t="s">
+        <v>13</v>
+      </c>
+      <c r="E217" t="s">
+        <v>316</v>
+      </c>
+      <c r="F217" t="s">
+        <v>54</v>
+      </c>
+      <c r="G217" t="s">
+        <v>322</v>
+      </c>
+      <c r="H217" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>315</v>
+      </c>
+      <c r="B218" t="s">
+        <v>63</v>
+      </c>
+      <c r="C218" t="s">
+        <v>317</v>
+      </c>
+      <c r="D218" t="s">
+        <v>14</v>
+      </c>
+      <c r="E218" t="s">
+        <v>247</v>
+      </c>
+      <c r="G218" t="s">
+        <v>252</v>
+      </c>
+      <c r="H218" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>29</v>
+      </c>
+      <c r="B219" t="s">
+        <v>5</v>
+      </c>
+      <c r="C219" t="s">
+        <v>144</v>
+      </c>
+      <c r="D219" t="s">
+        <v>14</v>
+      </c>
+      <c r="E219" t="s">
+        <v>43</v>
+      </c>
+      <c r="G219" t="s">
+        <v>44</v>
+      </c>
+      <c r="H219" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>32</v>
+      </c>
+      <c r="B220" t="s">
+        <v>241</v>
+      </c>
+      <c r="C220" t="s">
+        <v>242</v>
+      </c>
+      <c r="D220" t="s">
+        <v>14</v>
+      </c>
+      <c r="E220" t="s">
+        <v>313</v>
+      </c>
+      <c r="G220" t="s">
+        <v>321</v>
+      </c>
+      <c r="H220" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>32</v>
+      </c>
+      <c r="B221" t="s">
+        <v>5</v>
+      </c>
+      <c r="C221" t="s">
+        <v>95</v>
+      </c>
+      <c r="D221" t="s">
+        <v>14</v>
+      </c>
+      <c r="E221" t="s">
+        <v>297</v>
+      </c>
+      <c r="G221" t="s">
+        <v>305</v>
+      </c>
+      <c r="H221" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>32</v>
+      </c>
+      <c r="B222" t="s">
+        <v>23</v>
+      </c>
+      <c r="C222" t="s">
+        <v>188</v>
+      </c>
+      <c r="D222" t="s">
+        <v>14</v>
+      </c>
+      <c r="E222" t="s">
+        <v>280</v>
+      </c>
+      <c r="F222" t="s">
+        <v>155</v>
+      </c>
+      <c r="G222" t="s">
+        <v>285</v>
+      </c>
+      <c r="H222" s="1">
+        <v>46106</v>
+      </c>
+      <c r="L222" s="2"/>
+    </row>
+    <row r="223" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>29</v>
+      </c>
+      <c r="B223" t="s">
+        <v>3</v>
+      </c>
+      <c r="C223" t="s">
+        <v>26</v>
+      </c>
+      <c r="D223" t="s">
+        <v>13</v>
+      </c>
+      <c r="E223" t="s">
+        <v>31</v>
+      </c>
+      <c r="G223" t="s">
+        <v>30</v>
+      </c>
+      <c r="H223" s="1">
+        <v>46106</v>
+      </c>
+      <c r="J223" s="2"/>
+    </row>
+    <row r="224" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B224" t="s">
+        <v>23</v>
+      </c>
+      <c r="C224" t="s">
+        <v>126</v>
+      </c>
+      <c r="E224" t="s">
+        <v>319</v>
+      </c>
+      <c r="F224" t="s">
+        <v>227</v>
+      </c>
+      <c r="G224" t="s">
+        <v>323</v>
+      </c>
+      <c r="H224" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E225" t="s">
+        <v>318</v>
+      </c>
+      <c r="G225" t="s">
+        <v>324</v>
+      </c>
+      <c r="H225" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>29</v>
+      </c>
+      <c r="D226" t="s">
+        <v>13</v>
+      </c>
+      <c r="E226" t="s">
+        <v>309</v>
+      </c>
+      <c r="F226" t="s">
+        <v>171</v>
+      </c>
+      <c r="G226" t="s">
+        <v>309</v>
+      </c>
+      <c r="H226" s="1">
+        <v>46106</v>
       </c>
     </row>
   </sheetData>

--- a/vehicles.xlsx
+++ b/vehicles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandyeyster/Sandys documents/GEO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F018A79-F4D7-E44B-A005-3BF40C5B456F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFE051E-8E2D-CB44-9086-BBE60262521F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2440" yWindow="760" windowWidth="28660" windowHeight="20100" xr2:uid="{84ED28A7-E32C-0C4A-A6A7-0B027FAD99D7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="326">
   <si>
     <t>Color</t>
   </si>
@@ -986,9 +986,6 @@
     <t>Beige</t>
   </si>
   <si>
-    <t>BLack</t>
-  </si>
-  <si>
     <t>NJ U72RZF</t>
   </si>
   <si>
@@ -1014,6 +1011,12 @@
   </si>
   <si>
     <t>DC15779</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US Marshals  </t>
   </si>
 </sst>
 </file>
@@ -1395,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC0DC25-20B3-834F-98DA-243C4E7C4E30}">
-  <dimension ref="A1:P226"/>
+  <dimension ref="A1:P241"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -6307,7 +6310,7 @@
         <v>54</v>
       </c>
       <c r="G211" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H211" s="1">
         <v>46106</v>
@@ -6383,7 +6386,7 @@
         <v>313</v>
       </c>
       <c r="G214" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H214" s="1">
         <v>46106</v>
@@ -6394,10 +6397,10 @@
         <v>29</v>
       </c>
       <c r="B215" t="s">
+        <v>4</v>
+      </c>
+      <c r="C215" t="s">
         <v>143</v>
-      </c>
-      <c r="C215" t="s">
-        <v>274</v>
       </c>
       <c r="D215" t="s">
         <v>13</v>
@@ -6449,13 +6452,13 @@
         <v>13</v>
       </c>
       <c r="E217" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F217" t="s">
         <v>54</v>
       </c>
       <c r="G217" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H217" s="1">
         <v>46106</v>
@@ -6463,13 +6466,13 @@
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>315</v>
+        <v>32</v>
       </c>
       <c r="B218" t="s">
         <v>63</v>
       </c>
       <c r="C218" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D218" t="s">
         <v>14</v>
@@ -6524,7 +6527,7 @@
         <v>313</v>
       </c>
       <c r="G220" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H220" s="1">
         <v>46106</v>
@@ -6612,13 +6615,13 @@
         <v>126</v>
       </c>
       <c r="E224" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F224" t="s">
         <v>227</v>
       </c>
       <c r="G224" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H224" s="1">
         <v>46106</v>
@@ -6626,10 +6629,10 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="E225" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G225" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H225" s="1">
         <v>46106</v>
@@ -6654,6 +6657,242 @@
       <c r="H226" s="1">
         <v>46106</v>
       </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>32</v>
+      </c>
+      <c r="B227" t="s">
+        <v>23</v>
+      </c>
+      <c r="C227" t="s">
+        <v>188</v>
+      </c>
+      <c r="D227" t="s">
+        <v>14</v>
+      </c>
+      <c r="E227" t="s">
+        <v>280</v>
+      </c>
+      <c r="G227" t="s">
+        <v>285</v>
+      </c>
+      <c r="H227" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>324</v>
+      </c>
+      <c r="B228" t="s">
+        <v>3</v>
+      </c>
+      <c r="C228" t="s">
+        <v>26</v>
+      </c>
+      <c r="D228" t="s">
+        <v>13</v>
+      </c>
+      <c r="E228" t="s">
+        <v>315</v>
+      </c>
+      <c r="G228" t="s">
+        <v>321</v>
+      </c>
+      <c r="H228" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>32</v>
+      </c>
+      <c r="B229" t="s">
+        <v>241</v>
+      </c>
+      <c r="C229" t="s">
+        <v>242</v>
+      </c>
+      <c r="D229" t="s">
+        <v>14</v>
+      </c>
+      <c r="E229" t="s">
+        <v>313</v>
+      </c>
+      <c r="G229" t="s">
+        <v>320</v>
+      </c>
+      <c r="H229" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>311</v>
+      </c>
+      <c r="B230" t="s">
+        <v>2</v>
+      </c>
+      <c r="C230" t="s">
+        <v>33</v>
+      </c>
+      <c r="D230" t="s">
+        <v>14</v>
+      </c>
+      <c r="E230" t="s">
+        <v>80</v>
+      </c>
+      <c r="G230" t="s">
+        <v>81</v>
+      </c>
+      <c r="H230" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>29</v>
+      </c>
+      <c r="B231" t="s">
+        <v>4</v>
+      </c>
+      <c r="C231" t="s">
+        <v>143</v>
+      </c>
+      <c r="D231" t="s">
+        <v>13</v>
+      </c>
+      <c r="E231" t="s">
+        <v>198</v>
+      </c>
+      <c r="G231" t="s">
+        <v>200</v>
+      </c>
+      <c r="H231" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>32</v>
+      </c>
+      <c r="B232" t="s">
+        <v>6</v>
+      </c>
+      <c r="C232" t="s">
+        <v>38</v>
+      </c>
+      <c r="D232" t="s">
+        <v>13</v>
+      </c>
+      <c r="E232" t="s">
+        <v>230</v>
+      </c>
+      <c r="G232" t="s">
+        <v>236</v>
+      </c>
+      <c r="H232" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>32</v>
+      </c>
+      <c r="B233" t="s">
+        <v>63</v>
+      </c>
+      <c r="C233" t="s">
+        <v>316</v>
+      </c>
+      <c r="D233" t="s">
+        <v>14</v>
+      </c>
+      <c r="E233" t="s">
+        <v>247</v>
+      </c>
+      <c r="G233" t="s">
+        <v>252</v>
+      </c>
+      <c r="H233" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>29</v>
+      </c>
+      <c r="B234" t="s">
+        <v>5</v>
+      </c>
+      <c r="C234" t="s">
+        <v>144</v>
+      </c>
+      <c r="D234" t="s">
+        <v>14</v>
+      </c>
+      <c r="E234" t="s">
+        <v>43</v>
+      </c>
+      <c r="F234" t="s">
+        <v>325</v>
+      </c>
+      <c r="G234" t="s">
+        <v>44</v>
+      </c>
+      <c r="H234" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>32</v>
+      </c>
+      <c r="B235" t="s">
+        <v>5</v>
+      </c>
+      <c r="C235" t="s">
+        <v>95</v>
+      </c>
+      <c r="D235" t="s">
+        <v>14</v>
+      </c>
+      <c r="E235" t="s">
+        <v>297</v>
+      </c>
+      <c r="G235" t="s">
+        <v>305</v>
+      </c>
+      <c r="H235" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>29</v>
+      </c>
+      <c r="B236" t="s">
+        <v>3</v>
+      </c>
+      <c r="C236" t="s">
+        <v>26</v>
+      </c>
+      <c r="D236" t="s">
+        <v>13</v>
+      </c>
+      <c r="E236" t="s">
+        <v>31</v>
+      </c>
+      <c r="G236" t="s">
+        <v>30</v>
+      </c>
+      <c r="H236" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="241" spans="15:15" x14ac:dyDescent="0.2">
+      <c r="O241" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J186" xr:uid="{8FC0DC25-20B3-834F-98DA-243C4E7C4E30}">
